--- a/trades/rise_strategy_tracking_v1.xlsx
+++ b/trades/rise_strategy_tracking_v1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O98"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,45 +461,55 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Max_Price</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Profit_Pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Max_Profit_Pct</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Disparity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MA40</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MA90</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MA185</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Conv_Score</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Bowl_Count</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Touch_Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Small_Neg_Candles</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -508,7 +518,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,47 +528,53 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>XRP/KRW</t>
+          <t>SAND/KRW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2114</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>2114</v>
+        <v>118</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H2" t="n">
-        <v>2073.125</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2072.388888888889</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2496.924324324325</v>
+        <v>2.602797596695451</v>
       </c>
       <c r="K2" t="n">
+        <v>115.275</v>
+      </c>
+      <c r="L2" t="n">
+        <v>118.3555555555556</v>
+      </c>
+      <c r="M2" t="n">
+        <v>157.9189189189189</v>
+      </c>
+      <c r="N2" t="n">
         <v>10</v>
       </c>
-      <c r="L2" t="n">
-        <v>50</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="n">
+        <v>50</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -567,7 +583,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -577,7 +593,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QTUM/KRW</t>
+          <t>AWE/KRW</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -586,38 +602,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1470</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1470</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1370.425</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1353.133333333333</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1708.843243243243</v>
+        <v>2.303834876427843</v>
       </c>
       <c r="K3" t="n">
+        <v>79.85499999999999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>81.73811111111111</v>
+      </c>
+      <c r="M3" t="n">
+        <v>83.79978378378379</v>
+      </c>
+      <c r="N3" t="n">
         <v>8</v>
       </c>
-      <c r="L3" t="n">
-        <v>50</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>50</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -626,7 +648,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -636,7 +658,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ICX/KRW</t>
+          <t>GHX/KRW</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -645,38 +667,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>57.43</v>
+        <v>13.05</v>
       </c>
       <c r="F4" t="n">
-        <v>57.43</v>
+        <v>13.05</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>13.05</v>
       </c>
       <c r="H4" t="n">
-        <v>55.95800000000001</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>55.02111111111112</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>71.36767567567568</v>
+        <v>0.1836402984940497</v>
       </c>
       <c r="K4" t="n">
+        <v>12.3505</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12.37322222222222</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15.02767567567568</v>
+      </c>
+      <c r="N4" t="n">
         <v>9</v>
       </c>
-      <c r="L4" t="n">
-        <v>50</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -685,7 +713,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -695,47 +723,53 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ELF/KRW</t>
+          <t>CBK/KRW</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>381</v>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>381</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="H5" t="n">
-        <v>117.725</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>117.5555555555556</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>128.972972972973</v>
+        <v>0.4440418201259319</v>
       </c>
       <c r="K5" t="n">
+        <v>375.75</v>
+      </c>
+      <c r="L5" t="n">
+        <v>374.0888888888889</v>
+      </c>
+      <c r="M5" t="n">
+        <v>443.3189189189189</v>
+      </c>
+      <c r="N5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" t="n">
-        <v>50</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>50</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -744,7 +778,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -754,7 +788,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GLM/KRW</t>
+          <t>SNX/KRW</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -763,38 +797,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>215</v>
+        <v>496</v>
       </c>
       <c r="F6" t="n">
-        <v>215</v>
+        <v>496</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="H6" t="n">
-        <v>199.9</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>204.3666666666667</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>272.4108108108108</v>
+        <v>0.5595987646932096</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>461.525</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>464.1222222222222</v>
+      </c>
+      <c r="M6" t="n">
+        <v>588.0378378378379</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>50</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -803,7 +843,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -813,47 +853,53 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>POWR/KRW</t>
+          <t>MANA/KRW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>97.05</v>
+        <v>143</v>
       </c>
       <c r="F7" t="n">
-        <v>97.05</v>
+        <v>143</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="H7" t="n">
-        <v>97.10899999999999</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>95.52922222222222</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>111.9525405405406</v>
+        <v>0.2849234776945597</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>136.1</v>
       </c>
       <c r="L7" t="n">
-        <v>50</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>136.4888888888889</v>
+      </c>
+      <c r="M7" t="n">
+        <v>177.0864864864865</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>50</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -862,7 +908,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -872,7 +918,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SNT/KRW</t>
+          <t>LPT/KRW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -881,38 +927,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15.23</v>
+        <v>3301</v>
       </c>
       <c r="F8" t="n">
-        <v>15.23</v>
+        <v>3301</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3301</v>
       </c>
       <c r="H8" t="n">
-        <v>14.88375</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>14.97388888888889</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>18.34508108108108</v>
+        <v>2.451378250327184</v>
       </c>
       <c r="K8" t="n">
+        <v>3205.025</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3285.566666666667</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4175.254054054054</v>
+      </c>
+      <c r="N8" t="n">
         <v>9</v>
       </c>
-      <c r="L8" t="n">
-        <v>50</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -921,7 +973,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -931,47 +983,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADA/KRW</t>
+          <t>SUSHI/KRW</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="F9" t="n">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="H9" t="n">
-        <v>376.825</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>386.8</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>481.6054054054054</v>
+        <v>3.595661746129141</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>318.925</v>
       </c>
       <c r="L9" t="n">
-        <v>50</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>307.8555555555556</v>
+      </c>
+      <c r="M9" t="n">
+        <v>398.3405405405405</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -980,7 +1038,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -990,47 +1048,53 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BAT/KRW</t>
+          <t>PUNDIX/KRW</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="F10" t="n">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="H10" t="n">
-        <v>151.175</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>154.5222222222222</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>229.8054054054054</v>
+        <v>0.7708816419162281</v>
       </c>
       <c r="K10" t="n">
+        <v>223.475</v>
+      </c>
+      <c r="L10" t="n">
+        <v>225.2111111111111</v>
+      </c>
+      <c r="M10" t="n">
+        <v>285.3243243243243</v>
+      </c>
+      <c r="N10" t="n">
         <v>10</v>
       </c>
-      <c r="L10" t="n">
-        <v>50</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1039,7 +1103,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1049,7 +1113,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CVC/KRW</t>
+          <t>SIX/KRW</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1058,38 +1122,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>46.5</v>
+        <v>13.8</v>
       </c>
       <c r="F11" t="n">
-        <v>46.5</v>
+        <v>13.8</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="H11" t="n">
-        <v>45.967</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>46.10177777777778</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>56.17086486486486</v>
+        <v>1.087908637159964</v>
       </c>
       <c r="K11" t="n">
+        <v>13.2995</v>
+      </c>
+      <c r="L11" t="n">
+        <v>13.44577777777778</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15.87778378378378</v>
+      </c>
+      <c r="N11" t="n">
         <v>10</v>
       </c>
-      <c r="L11" t="n">
-        <v>50</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="n">
+        <v>50</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1098,7 +1168,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1108,7 +1178,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VET/KRW</t>
+          <t>POL/KRW</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1117,38 +1187,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.88</v>
+        <v>141</v>
       </c>
       <c r="F12" t="n">
-        <v>10.88</v>
+        <v>141</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H12" t="n">
-        <v>10.79675</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>10.80312222222222</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>14.01270810810811</v>
+        <v>3.543979504696841</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>138.05</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>143.1222222222222</v>
+      </c>
+      <c r="M12" t="n">
+        <v>164.1081081081081</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O12" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>50</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1157,7 +1233,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-14 00:13</t>
+          <t>2026-05-15 00:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1167,7 +1243,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IOST/KRW</t>
+          <t>META/KRW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1176,38 +1252,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.725</v>
+        <v>14.51</v>
       </c>
       <c r="F13" t="n">
-        <v>1.725</v>
+        <v>14.51</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>14.51</v>
       </c>
       <c r="H13" t="n">
-        <v>1.635</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1.674333333333333</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.098740540540541</v>
+        <v>0.2703342596761479</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>14.35225</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>14.31355555555556</v>
+      </c>
+      <c r="M13" t="n">
+        <v>15.45043243243243</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>50</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1216,7 +1298,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1226,47 +1308,53 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CTC/KRW</t>
+          <t>XTZ/KRW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229</v>
+        <v>560</v>
       </c>
       <c r="F14" t="n">
-        <v>229</v>
+        <v>560</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="H14" t="n">
-        <v>221.1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>227.5555555555555</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>312.545945945946</v>
+        <v>1.332931242460798</v>
       </c>
       <c r="K14" t="n">
+        <v>545.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>552.6666666666666</v>
+      </c>
+      <c r="M14" t="n">
+        <v>656.7027027027027</v>
+      </c>
+      <c r="N14" t="n">
         <v>10</v>
       </c>
-      <c r="L14" t="n">
-        <v>50</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="n">
+        <v>50</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1275,7 +1363,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1285,47 +1373,53 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CKB/KRW</t>
+          <t>MLK/KRW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.38</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2.38</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2654</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.248233333333333</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.982172972972973</v>
+        <v>1.533041568059061</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>77.297</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>78.50044444444444</v>
+      </c>
+      <c r="M15" t="n">
+        <v>94.5881081081081</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O15" t="n">
+        <v>50</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1334,7 +1428,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1344,47 +1438,53 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AERGO/KRW</t>
+          <t>ATOM/KRW</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>81.01000000000001</v>
+        <v>3026</v>
       </c>
       <c r="F16" t="n">
-        <v>81.01000000000001</v>
+        <v>3026</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3026</v>
       </c>
       <c r="H16" t="n">
-        <v>81.727</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>81.33677777777777</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>85.81794594594595</v>
+        <v>0.1590396673013655</v>
       </c>
       <c r="K16" t="n">
+        <v>2784.875</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2789.311111111111</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3094.697297297297</v>
+      </c>
+      <c r="N16" t="n">
         <v>8</v>
       </c>
-      <c r="L16" t="n">
-        <v>50</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="n">
+        <v>50</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1393,7 +1493,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1403,47 +1503,53 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UMA/KRW</t>
+          <t>KSM/KRW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>725</v>
+        <v>8090</v>
       </c>
       <c r="F17" t="n">
-        <v>725</v>
+        <v>8090</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>8090</v>
       </c>
       <c r="H17" t="n">
-        <v>680.25</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>662.8222222222222</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>889.7621621621622</v>
+        <v>3.237011115026105</v>
       </c>
       <c r="K17" t="n">
+        <v>7162.125</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6937.555555555556</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9077.513513513513</v>
+      </c>
+      <c r="N17" t="n">
         <v>8</v>
       </c>
-      <c r="L17" t="n">
-        <v>50</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" t="n">
+        <v>50</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1452,7 +1558,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1462,47 +1568,53 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAND/KRW</t>
+          <t>EGLD/KRW</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115</v>
+        <v>6495</v>
       </c>
       <c r="F18" t="n">
-        <v>115</v>
+        <v>6495</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>6495</v>
       </c>
       <c r="H18" t="n">
-        <v>115.2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>118.3222222222222</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>157.9027027027027</v>
+        <v>0.8453414481339007</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>6154.75</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>6207.222222222223</v>
+      </c>
+      <c r="M18" t="n">
+        <v>8025.405405405405</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>50</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1511,7 +1623,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1521,7 +1633,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AWE/KRW</t>
+          <t>MED/KRW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1530,38 +1642,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>82.77</v>
+        <v>3.212</v>
       </c>
       <c r="F19" t="n">
-        <v>82.77</v>
+        <v>3.212</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3.212</v>
       </c>
       <c r="H19" t="n">
-        <v>79.6755</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>82.28822222222223</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>83.89259459459458</v>
+        <v>2.016092448411084</v>
       </c>
       <c r="K19" t="n">
+        <v>3.239925</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3.306588888888889</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.666681081081081</v>
+      </c>
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="L19" t="n">
-        <v>50</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>3</v>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" t="n">
+        <v>50</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1570,7 +1688,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1580,47 +1698,53 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GHX/KRW</t>
+          <t>1INCH/KRW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>13.18</v>
+        <v>146</v>
       </c>
       <c r="F20" t="n">
-        <v>13.18</v>
+        <v>146</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H20" t="n">
-        <v>12.35375</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>12.37466666666667</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>15.02837837837838</v>
+        <v>1.183009130607371</v>
       </c>
       <c r="K20" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>139.9444444444445</v>
+      </c>
+      <c r="M20" t="n">
+        <v>186.4378378378378</v>
+      </c>
+      <c r="N20" t="n">
         <v>9</v>
       </c>
-      <c r="L20" t="n">
-        <v>50</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" t="n">
+        <v>50</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1629,7 +1753,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1639,47 +1763,53 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CBK/KRW</t>
+          <t>MINA/KRW</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>383</v>
+        <v>97.13</v>
       </c>
       <c r="F21" t="n">
-        <v>383</v>
+        <v>97.13</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>97.13</v>
       </c>
       <c r="H21" t="n">
-        <v>375.425</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>374.1777777777778</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>444.5243243243243</v>
+        <v>2.335895676220473</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>89.80225</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>87.75244444444445</v>
+      </c>
+      <c r="M21" t="n">
+        <v>111.2338378378378</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>50</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1688,7 +1818,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1698,7 +1828,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GRT/KRW</t>
+          <t>XRP/KRW</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1707,38 +1837,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>41.24</v>
+        <v>2169</v>
       </c>
       <c r="F22" t="n">
-        <v>41.24</v>
+        <v>2169</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2169</v>
       </c>
       <c r="H22" t="n">
-        <v>37.41075</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>37.96644444444444</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>49.9692972972973</v>
+        <v>0.3286793868581832</v>
       </c>
       <c r="K22" t="n">
+        <v>2079.925</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2073.111111111111</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2489.151351351351</v>
+      </c>
+      <c r="N22" t="n">
         <v>10</v>
       </c>
-      <c r="L22" t="n">
-        <v>50</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" t="n">
+        <v>50</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1747,7 +1883,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1757,7 +1893,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SNX/KRW</t>
+          <t>QTUM/KRW</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1766,38 +1902,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>497</v>
+        <v>1470</v>
       </c>
       <c r="F23" t="n">
-        <v>497</v>
+        <v>1470</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1470</v>
       </c>
       <c r="H23" t="n">
-        <v>461.55</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>464.1333333333333</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>588.0432432432433</v>
+        <v>1.277898211558347</v>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>1370.425</v>
       </c>
       <c r="L23" t="n">
-        <v>50</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>1353.133333333333</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1708.843243243243</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>50</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1806,7 +1948,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1816,47 +1958,53 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MANA/KRW</t>
+          <t>ELF/KRW</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="F24" t="n">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H24" t="n">
-        <v>136.1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>136.4888888888889</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>177.0864864864865</v>
+        <v>0.132337650061439</v>
       </c>
       <c r="K24" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="L24" t="n">
+        <v>117.5444444444445</v>
+      </c>
+      <c r="M24" t="n">
+        <v>128.9675675675676</v>
+      </c>
+      <c r="N24" t="n">
         <v>9</v>
       </c>
-      <c r="L24" t="n">
-        <v>50</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" t="n">
+        <v>50</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1865,7 +2013,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1875,7 +2023,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LPT/KRW</t>
+          <t>GLM/KRW</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1884,38 +2032,44 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3303</v>
+        <v>210</v>
       </c>
       <c r="F25" t="n">
-        <v>3303</v>
+        <v>210</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H25" t="n">
-        <v>3205.075</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3285.588888888889</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>4175.264864864865</v>
+        <v>2.220197955188159</v>
       </c>
       <c r="K25" t="n">
-        <v>9</v>
+        <v>199.775</v>
       </c>
       <c r="L25" t="n">
-        <v>50</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>204.3111111111111</v>
+      </c>
+      <c r="M25" t="n">
+        <v>272.3837837837838</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>50</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1924,7 +2078,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1934,7 +2088,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUSHI/KRW</t>
+          <t>ZIL/KRW</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1943,38 +2097,44 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>349</v>
+        <v>6.236</v>
       </c>
       <c r="F26" t="n">
-        <v>349</v>
+        <v>6.236</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>6.236</v>
       </c>
       <c r="H26" t="n">
-        <v>319.075</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>307.9222222222222</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>398.3729729729729</v>
+        <v>0.04730407959908729</v>
       </c>
       <c r="K26" t="n">
-        <v>8</v>
+        <v>6.068825</v>
       </c>
       <c r="L26" t="n">
-        <v>50</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>6.065955555555555</v>
+      </c>
+      <c r="M26" t="n">
+        <v>7.018962162162162</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O26" t="n">
+        <v>50</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -1983,7 +2143,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,47 +2153,53 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PUNDIX/KRW</t>
+          <t>POWR/KRW</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="F27" t="n">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H27" t="n">
-        <v>223.25</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>225.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>286.5243243243243</v>
+        <v>1.652994214651095</v>
       </c>
       <c r="K27" t="n">
-        <v>10</v>
+        <v>97.10775</v>
       </c>
       <c r="L27" t="n">
-        <v>50</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>95.52866666666667</v>
+      </c>
+      <c r="M27" t="n">
+        <v>111.9522702702703</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>50</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2042,7 +2208,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-14 00:14</t>
+          <t>2026-05-15 00:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2052,47 +2218,53 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CELR/KRW</t>
+          <t>SNT/KRW</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4.291</v>
+        <v>15.34</v>
       </c>
       <c r="F28" t="n">
-        <v>4.291</v>
+        <v>15.34</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>15.34</v>
       </c>
       <c r="H28" t="n">
-        <v>3.981225</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3.880222222222222</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>4.869005405405406</v>
+        <v>0.5917225618804689</v>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>14.8865</v>
       </c>
       <c r="L28" t="n">
-        <v>50</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>14.97511111111111</v>
+      </c>
+      <c r="M28" t="n">
+        <v>18.34567567567568</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O28" t="n">
+        <v>50</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2101,7 +2273,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-14 00:15</t>
+          <t>2026-05-15 00:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2111,47 +2283,53 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SIX/KRW</t>
+          <t>BAT/KRW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>13.94</v>
+        <v>155</v>
       </c>
       <c r="F29" t="n">
-        <v>13.94</v>
+        <v>155</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H29" t="n">
-        <v>13.33225</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>13.45611111111111</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>15.93459459459459</v>
+        <v>1.733833177132161</v>
       </c>
       <c r="K29" t="n">
+        <v>151.45</v>
+      </c>
+      <c r="L29" t="n">
+        <v>154.1222222222222</v>
+      </c>
+      <c r="M29" t="n">
+        <v>228.827027027027</v>
+      </c>
+      <c r="N29" t="n">
         <v>10</v>
       </c>
-      <c r="L29" t="n">
-        <v>50</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" t="n">
+        <v>50</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2160,7 +2338,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-14 00:15</t>
+          <t>2026-05-15 00:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2170,47 +2348,53 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>XLM/KRW</t>
+          <t>CVC/KRW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>237</v>
+        <v>47.5</v>
       </c>
       <c r="F30" t="n">
-        <v>237</v>
+        <v>47.5</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="H30" t="n">
-        <v>242.3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>241.9</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>286.9945945945946</v>
+        <v>0.01688626856887497</v>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>46.052</v>
       </c>
       <c r="L30" t="n">
-        <v>50</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>46.05977777777778</v>
+      </c>
+      <c r="M30" t="n">
+        <v>55.93902702702703</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O30" t="n">
+        <v>50</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2219,7 +2403,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-14 00:15</t>
+          <t>2026-05-15 00:09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2229,47 +2413,53 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>META/KRW</t>
+          <t>VET/KRW</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>14.6</v>
+        <v>10.97</v>
       </c>
       <c r="F31" t="n">
-        <v>14.6</v>
+        <v>10.97</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>10.97</v>
       </c>
       <c r="H31" t="n">
-        <v>14.344</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>14.30266666666667</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>15.48135135135135</v>
+        <v>0.047023025316199</v>
       </c>
       <c r="K31" t="n">
-        <v>8</v>
+        <v>10.79175</v>
       </c>
       <c r="L31" t="n">
-        <v>50</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>10.78667777777778</v>
+      </c>
+      <c r="M31" t="n">
+        <v>13.93232972972973</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>50</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2278,7 +2468,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-14 00:15</t>
+          <t>2026-05-15 00:10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2288,47 +2478,53 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XTZ/KRW</t>
+          <t>CRO/KRW</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>559</v>
+        <v>112</v>
       </c>
       <c r="F32" t="n">
-        <v>559</v>
+        <v>112</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="H32" t="n">
-        <v>545.275</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>552.6555555555556</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>656.6972972972973</v>
+        <v>3.321749795584631</v>
       </c>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>105.1</v>
       </c>
       <c r="L32" t="n">
-        <v>50</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>108.7111111111111</v>
+      </c>
+      <c r="M32" t="n">
+        <v>126.9297297297297</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
-      </c>
-      <c r="O32" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O32" t="n">
+        <v>50</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2337,7 +2533,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-14 00:15</t>
+          <t>2026-05-15 00:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2347,7 +2543,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MLK/KRW</t>
+          <t>MBL/KRW</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2356,38 +2552,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>79.7</v>
+        <v>1.424</v>
       </c>
       <c r="F33" t="n">
-        <v>79.7</v>
+        <v>1.424</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.424</v>
       </c>
       <c r="H33" t="n">
-        <v>77.33500000000001</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>78.51733333333333</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>94.59632432432433</v>
+        <v>1.318906840566384</v>
       </c>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>1.42075</v>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>1.402255555555556</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.598675675675676</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
-      </c>
-      <c r="O33" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>50</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2396,7 +2598,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-14 00:15</t>
+          <t>2026-05-15 00:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2406,47 +2608,53 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MED/KRW</t>
+          <t>EL/KRW</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3.244</v>
+        <v>2.85</v>
       </c>
       <c r="F34" t="n">
-        <v>3.244</v>
+        <v>2.85</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="H34" t="n">
-        <v>3.240725</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3.306944444444444</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>3.666854054054054</v>
+        <v>1.52050585037229</v>
       </c>
       <c r="K34" t="n">
+        <v>2.77745</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.820333333333334</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.115913513513514</v>
+      </c>
+      <c r="N34" t="n">
         <v>8</v>
       </c>
-      <c r="L34" t="n">
-        <v>50</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>2</v>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" t="n">
+        <v>50</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2455,7 +2663,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-14 00:15</t>
+          <t>2026-05-15 00:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2465,7 +2673,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1INCH/KRW</t>
+          <t>HIVE/KRW</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2474,38 +2682,44 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>146</v>
+        <v>95.11</v>
       </c>
       <c r="F35" t="n">
-        <v>146</v>
+        <v>95.11</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>95.11</v>
       </c>
       <c r="H35" t="n">
-        <v>141.25</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>139.8555555555556</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>187.3189189189189</v>
+        <v>0.843572006366324</v>
       </c>
       <c r="K35" t="n">
-        <v>9</v>
+        <v>92.34349999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>50</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>93.12911111111111</v>
+      </c>
+      <c r="M35" t="n">
+        <v>119.4411891891892</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O35" t="n">
+        <v>50</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2514,7 +2728,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-14 00:15</t>
+          <t>2026-05-15 00:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2524,47 +2738,53 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MINA/KRW</t>
+          <t>CKB/KRW</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>95.86</v>
+        <v>2.403</v>
       </c>
       <c r="F36" t="n">
-        <v>95.86</v>
+        <v>2.403</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2.403</v>
       </c>
       <c r="H36" t="n">
-        <v>89.43474999999999</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>87.76677777777778</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>111.9010810810811</v>
+        <v>1.13189633431738</v>
       </c>
       <c r="K36" t="n">
-        <v>8</v>
+        <v>2.2724</v>
       </c>
       <c r="L36" t="n">
-        <v>50</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>2.246966666666667</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.9684</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
-      </c>
-      <c r="O36" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O36" t="n">
+        <v>50</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2573,7 +2793,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-14 00:16</t>
+          <t>2026-05-15 00:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2583,47 +2803,53 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>REQ/KRW</t>
+          <t>UMA/KRW</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>104</v>
+        <v>732</v>
       </c>
       <c r="F37" t="n">
-        <v>104</v>
+        <v>732</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="H37" t="n">
-        <v>106.58575</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>102.2116666666667</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>129.5245945945946</v>
+        <v>3.2212215737573</v>
       </c>
       <c r="K37" t="n">
+        <v>683.875</v>
+      </c>
+      <c r="L37" t="n">
+        <v>662.5333333333333</v>
+      </c>
+      <c r="M37" t="n">
+        <v>885.5783783783784</v>
+      </c>
+      <c r="N37" t="n">
         <v>8</v>
       </c>
-      <c r="L37" t="n">
-        <v>50</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>2</v>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" t="n">
+        <v>50</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2632,7 +2858,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-14 00:16</t>
+          <t>2026-05-15 00:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2642,7 +2868,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GMT/KRW</t>
+          <t>UOS/KRW</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2651,38 +2877,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>18.19</v>
+        <v>9.590999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>18.19</v>
+        <v>9.590999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>9.590999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>16.7375</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>16.56155555555555</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>20.77897297297297</v>
+        <v>1.829053751708678</v>
       </c>
       <c r="K38" t="n">
-        <v>9</v>
+        <v>9.229050000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>50</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>9.063277777777778</v>
+      </c>
+      <c r="M38" t="n">
+        <v>11.94015675675676</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
-      </c>
-      <c r="O38" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>50</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2691,7 +2923,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-14 00:16</t>
+          <t>2026-05-15 00:11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2701,47 +2933,53 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WNCG/KRW</t>
+          <t>ACH/KRW</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>8.621</v>
+        <v>11.63</v>
       </c>
       <c r="F39" t="n">
-        <v>8.621</v>
+        <v>11.63</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>11.63</v>
       </c>
       <c r="H39" t="n">
-        <v>8.176424999999998</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>8.209766666666667</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>10.17374054054054</v>
+        <v>0.6612155235538137</v>
       </c>
       <c r="K39" t="n">
-        <v>10</v>
+        <v>10.310225</v>
       </c>
       <c r="L39" t="n">
-        <v>50</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>10.2425</v>
+      </c>
+      <c r="M39" t="n">
+        <v>12.07262162162162</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O39" t="n">
+        <v>50</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2750,7 +2988,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-14 00:16</t>
+          <t>2026-05-15 00:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2760,47 +2998,53 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>APT/KRW</t>
+          <t>JASMY/KRW</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1557</v>
+        <v>9.638999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>1557</v>
+        <v>9.638999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>9.638999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>1418.425</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1400.633333333333</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2064.578378378379</v>
+        <v>1.694328004052738</v>
       </c>
       <c r="K40" t="n">
-        <v>9</v>
+        <v>8.6096</v>
       </c>
       <c r="L40" t="n">
-        <v>50</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>8.466155555555556</v>
+      </c>
+      <c r="M40" t="n">
+        <v>9.44581081081081</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O40" t="n">
+        <v>50</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2809,7 +3053,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-14 00:16</t>
+          <t>2026-05-15 00:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2819,47 +3063,53 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ROA/KRW</t>
+          <t>CSPR/KRW</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6.756</v>
+        <v>4.338</v>
       </c>
       <c r="F41" t="n">
-        <v>6.756</v>
+        <v>4.338</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>4.338</v>
       </c>
       <c r="H41" t="n">
-        <v>6.53075</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>6.593099999999999</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>8.052967567567567</v>
+        <v>3.627169541426425</v>
       </c>
       <c r="K41" t="n">
-        <v>9</v>
+        <v>4.37175</v>
       </c>
       <c r="L41" t="n">
-        <v>50</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>4.536288888888889</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5.980648648648648</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O41" t="n">
+        <v>50</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2868,7 +3118,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-14 00:16</t>
+          <t>2026-05-15 00:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2878,47 +3128,53 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HFT/KRW</t>
+          <t>FANC/KRW</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23.03</v>
+        <v>2.101</v>
       </c>
       <c r="F42" t="n">
-        <v>23.03</v>
+        <v>2.101</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2.101</v>
       </c>
       <c r="H42" t="n">
-        <v>21.9275</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>21.89411111111111</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>33.51989189189189</v>
+        <v>3.148936391640994</v>
       </c>
       <c r="K42" t="n">
-        <v>9</v>
+        <v>2.06805</v>
       </c>
       <c r="L42" t="n">
-        <v>50</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>2.135288888888889</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.734594594594595</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O42" t="n">
+        <v>50</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2927,7 +3183,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-14 08:00</t>
+          <t>2026-05-15 00:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2937,47 +3193,53 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FIL/KRW</t>
+          <t>T/KRW</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1560</v>
+        <v>9.02</v>
       </c>
       <c r="F43" t="n">
-        <v>1554</v>
+        <v>9.02</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.3846153846153846</v>
+        <v>9.02</v>
       </c>
       <c r="H43" t="n">
-        <v>1424.475</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1390.055555555556</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1763.183783783784</v>
+        <v>3.365032639863324</v>
       </c>
       <c r="K43" t="n">
+        <v>9.151675000000001</v>
+      </c>
+      <c r="L43" t="n">
+        <v>9.470355555555555</v>
+      </c>
+      <c r="M43" t="n">
+        <v>11.96547027027027</v>
+      </c>
+      <c r="N43" t="n">
         <v>9</v>
       </c>
-      <c r="L43" t="n">
-        <v>50</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>2</v>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="O43" t="n">
+        <v>50</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -2986,7 +3248,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-14 08:00</t>
+          <t>2026-05-15 00:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2996,47 +3258,53 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SEI/KRW</t>
+          <t>MBX/KRW</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>99.06</v>
+        <v>61.21</v>
       </c>
       <c r="F44" t="n">
-        <v>98.84</v>
+        <v>61.21</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.2220876236624257</v>
+        <v>61.21</v>
       </c>
       <c r="H44" t="n">
-        <v>88.1255</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>92.35699999999999</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>135.7628648648649</v>
+        <v>3.997488600740933</v>
       </c>
       <c r="K44" t="n">
+        <v>59.88850000000001</v>
+      </c>
+      <c r="L44" t="n">
+        <v>62.38222222222222</v>
+      </c>
+      <c r="M44" t="n">
+        <v>86.6852972972973</v>
+      </c>
+      <c r="N44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" t="n">
-        <v>50</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" t="n">
+        <v>50</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3045,7 +3313,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-14 00:17</t>
+          <t>2026-05-15 00:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3055,7 +3323,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MOC/KRW</t>
+          <t>GMT/KRW</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3064,38 +3332,44 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>40.97</v>
+        <v>18.28</v>
       </c>
       <c r="F45" t="n">
-        <v>40.97</v>
+        <v>18.28</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>18.28</v>
       </c>
       <c r="H45" t="n">
-        <v>41.2875</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>41.25177777777778</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>46.78254054054054</v>
+        <v>1.582010795134146</v>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>16.8125</v>
       </c>
       <c r="L45" t="n">
-        <v>50</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>16.55066666666666</v>
+      </c>
+      <c r="M45" t="n">
+        <v>20.68167567567568</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
-      </c>
-      <c r="O45" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O45" t="n">
+        <v>50</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3104,7 +3378,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-14 00:17</t>
+          <t>2026-05-15 00:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3114,47 +3388,53 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CYBER/KRW</t>
+          <t>STAT/KRW</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>812</v>
+        <v>53.89</v>
       </c>
       <c r="F46" t="n">
-        <v>812</v>
+        <v>53.89</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>53.89</v>
       </c>
       <c r="H46" t="n">
-        <v>789.625</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>794.8444444444444</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>957.3405405405406</v>
+        <v>0.7622745586497198</v>
       </c>
       <c r="K46" t="n">
+        <v>44.04375</v>
+      </c>
+      <c r="L46" t="n">
+        <v>43.71055555555555</v>
+      </c>
+      <c r="M46" t="n">
+        <v>53.17956756756757</v>
+      </c>
+      <c r="N46" t="n">
         <v>9</v>
       </c>
-      <c r="L46" t="n">
-        <v>50</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>3</v>
-      </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" t="n">
+        <v>50</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3163,7 +3443,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-14 08:00</t>
+          <t>2026-05-15 00:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3173,7 +3453,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>METIS/KRW</t>
+          <t>ROA/KRW</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3182,38 +3462,44 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5525</v>
+        <v>6.594</v>
       </c>
       <c r="F47" t="n">
-        <v>5545</v>
+        <v>6.594</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3619909502262443</v>
+        <v>6.594</v>
       </c>
       <c r="H47" t="n">
-        <v>5183.525</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>4950.722222222223</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>6867.216216216216</v>
+        <v>1.014771818669477</v>
       </c>
       <c r="K47" t="n">
-        <v>8</v>
+        <v>6.520025</v>
       </c>
       <c r="L47" t="n">
-        <v>50</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>6.586866666666666</v>
+      </c>
+      <c r="M47" t="n">
+        <v>8.024810810810811</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
-      </c>
-      <c r="O47" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O47" t="n">
+        <v>50</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3222,7 +3508,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-14 08:00</t>
+          <t>2026-05-15 00:13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3232,47 +3518,53 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BIGTIME/KRW</t>
+          <t>AHT/KRW</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>20.35</v>
+        <v>2.315</v>
       </c>
       <c r="F48" t="n">
-        <v>20.3</v>
+        <v>2.315</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.2457002457002492</v>
+        <v>2.315</v>
       </c>
       <c r="H48" t="n">
-        <v>19.9515</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>20.12366666666667</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>26.20308108108108</v>
+        <v>0.0008501583723555123</v>
       </c>
       <c r="K48" t="n">
+        <v>2.287175</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.287155555555556</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.533551351351351</v>
+      </c>
+      <c r="N48" t="n">
         <v>9</v>
       </c>
-      <c r="L48" t="n">
-        <v>50</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="inlineStr">
+      <c r="O48" t="n">
+        <v>50</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3281,7 +3573,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-14 08:00</t>
+          <t>2026-05-15 00:13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3291,7 +3583,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ZETA/KRW</t>
+          <t>HFT/KRW</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3300,38 +3592,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>85.38</v>
+        <v>22.95</v>
       </c>
       <c r="F49" t="n">
-        <v>84.81999999999999</v>
+        <v>22.95</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.6558913094401526</v>
+        <v>22.95</v>
       </c>
       <c r="H49" t="n">
-        <v>82.24724999999999</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>79.26888888888888</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>97.40486486486488</v>
+        <v>0.6044786371754428</v>
       </c>
       <c r="K49" t="n">
-        <v>8</v>
+        <v>21.969</v>
       </c>
       <c r="L49" t="n">
-        <v>50</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>21.837</v>
+      </c>
+      <c r="M49" t="n">
+        <v>33.27648648648648</v>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
-      </c>
-      <c r="O49" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O49" t="n">
+        <v>50</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3340,7 +3638,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-14 08:00</t>
+          <t>2026-05-15 00:13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3350,47 +3648,53 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ARK/KRW</t>
+          <t>S/KRW</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>264</v>
+        <v>73.61</v>
       </c>
       <c r="F50" t="n">
-        <v>262</v>
+        <v>73.61</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.7575757575757576</v>
+        <v>73.61</v>
       </c>
       <c r="H50" t="n">
-        <v>257.825</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>259.7444444444445</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>327.2918918918919</v>
+        <v>3.251081430152944</v>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>67.15175000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>50</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>65.03733333333334</v>
+      </c>
+      <c r="M50" t="n">
+        <v>95.78805405405406</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O50" t="n">
+        <v>50</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3399,7 +3703,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-14 00:17</t>
+          <t>2026-05-15 00:13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3409,47 +3713,53 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HUNT/KRW</t>
+          <t>FIL/KRW</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>157</v>
+        <v>1557</v>
       </c>
       <c r="F51" t="n">
-        <v>157</v>
+        <v>1557</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1557</v>
       </c>
       <c r="H51" t="n">
-        <v>151.425</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>149.3444444444444</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>179.8648648648649</v>
+        <v>2.944782091316396</v>
       </c>
       <c r="K51" t="n">
-        <v>8</v>
+        <v>1432.225</v>
       </c>
       <c r="L51" t="n">
-        <v>50</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>1391.255555555555</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1752.172972972973</v>
       </c>
       <c r="N51" t="n">
-        <v>2</v>
-      </c>
-      <c r="O51" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O51" t="n">
+        <v>50</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3458,7 +3768,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3468,47 +3778,53 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MAGIC/KRW</t>
+          <t>SEI/KRW</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101</v>
+        <v>99.48</v>
       </c>
       <c r="F52" t="n">
-        <v>102</v>
+        <v>99.48</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9900990099009901</v>
+        <v>99.48</v>
       </c>
       <c r="H52" t="n">
-        <v>96.44225</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>94.7548888888889</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>120.0307027027027</v>
+        <v>3.830323687118912</v>
       </c>
       <c r="K52" t="n">
-        <v>8</v>
+        <v>88.66</v>
       </c>
       <c r="L52" t="n">
-        <v>50</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>92.19122222222221</v>
+      </c>
+      <c r="M52" t="n">
+        <v>134.8335675675676</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O52" t="n">
+        <v>50</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3517,7 +3833,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3527,47 +3843,53 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AUCTION/KRW</t>
+          <t>PYR/KRW</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>7210</v>
+        <v>417</v>
       </c>
       <c r="F53" t="n">
-        <v>7225</v>
+        <v>417</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2080443828016643</v>
+        <v>417</v>
       </c>
       <c r="H53" t="n">
-        <v>7144.625</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>7128.944444444444</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>7589.189189189189</v>
+        <v>4.833255597014931</v>
       </c>
       <c r="K53" t="n">
-        <v>8</v>
+        <v>408.075</v>
       </c>
       <c r="L53" t="n">
-        <v>50</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>428.8</v>
+      </c>
+      <c r="M53" t="n">
+        <v>586.0162162162162</v>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
-      </c>
-      <c r="O53" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O53" t="n">
+        <v>50</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3576,7 +3898,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3586,47 +3908,53 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LSK/KRW</t>
+          <t>BIGTIME/KRW</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>194</v>
+        <v>20.67</v>
       </c>
       <c r="F54" t="n">
-        <v>191</v>
+        <v>20.67</v>
       </c>
       <c r="G54" t="n">
-        <v>-1.54639175257732</v>
+        <v>20.67</v>
       </c>
       <c r="H54" t="n">
-        <v>191.75</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>192.8888888888889</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>242.2540540540541</v>
+        <v>0.390087005580966</v>
       </c>
       <c r="K54" t="n">
-        <v>10</v>
+        <v>20.00975</v>
       </c>
       <c r="L54" t="n">
-        <v>50</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>20.08811111111111</v>
+      </c>
+      <c r="M54" t="n">
+        <v>26.06805405405406</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O54" t="n">
+        <v>50</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3635,7 +3963,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3645,7 +3973,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SKL/KRW</t>
+          <t>ARK/KRW</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3654,38 +3982,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>10.3</v>
+        <v>266</v>
       </c>
       <c r="F55" t="n">
-        <v>10.09</v>
+        <v>266</v>
       </c>
       <c r="G55" t="n">
-        <v>-2.038834951456319</v>
+        <v>266</v>
       </c>
       <c r="H55" t="n">
-        <v>10.165825</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>9.967500000000001</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>13.3248972972973</v>
+        <v>0.7282176312074882</v>
       </c>
       <c r="K55" t="n">
-        <v>8</v>
+        <v>257.875</v>
       </c>
       <c r="L55" t="n">
-        <v>50</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>259.7666666666667</v>
+      </c>
+      <c r="M55" t="n">
+        <v>327.3027027027027</v>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
-      </c>
-      <c r="O55" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O55" t="n">
+        <v>50</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3694,7 +4028,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3704,47 +4038,53 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IQ/KRW</t>
+          <t>MAGIC/KRW</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.658</v>
+        <v>105</v>
       </c>
       <c r="F56" t="n">
-        <v>1.646</v>
+        <v>105</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.7237635705669488</v>
+        <v>105</v>
       </c>
       <c r="H56" t="n">
-        <v>1.62915</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1.6683</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>2.064183783783784</v>
+        <v>2.304780624336317</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>96.98425</v>
       </c>
       <c r="L56" t="n">
-        <v>50</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>94.79933333333334</v>
+      </c>
+      <c r="M56" t="n">
+        <v>119.5874594594595</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O56" t="n">
+        <v>50</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3753,7 +4093,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3763,47 +4103,53 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BEAM/KRW</t>
+          <t>LSK/KRW</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.943</v>
+        <v>190</v>
       </c>
       <c r="F57" t="n">
-        <v>2.86</v>
+        <v>190</v>
       </c>
       <c r="G57" t="n">
-        <v>-2.820251444104661</v>
+        <v>190</v>
       </c>
       <c r="H57" t="n">
-        <v>2.8941</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>2.9053</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3.752502702702702</v>
+        <v>0.6193823461627022</v>
       </c>
       <c r="K57" t="n">
-        <v>8</v>
+        <v>191.65</v>
       </c>
       <c r="L57" t="n">
-        <v>50</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>192.8444444444444</v>
+      </c>
+      <c r="M57" t="n">
+        <v>242.2324324324324</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O57" t="n">
+        <v>50</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3812,7 +4158,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3822,47 +4168,53 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ArchLoot/KRW</t>
+          <t>TT/KRW</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>11.22</v>
+        <v>1.345</v>
       </c>
       <c r="F58" t="n">
-        <v>11.09</v>
+        <v>1.345</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.158645276292342</v>
+        <v>1.345</v>
       </c>
       <c r="H58" t="n">
-        <v>10.99485</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>10.90954444444444</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>14.64615675675676</v>
+        <v>0.8408209150768781</v>
       </c>
       <c r="K58" t="n">
+        <v>1.325575</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.314522222222222</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.5084</v>
+      </c>
+      <c r="N58" t="n">
         <v>9</v>
       </c>
-      <c r="L58" t="n">
-        <v>50</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N58" t="n">
-        <v>2</v>
-      </c>
-      <c r="O58" t="inlineStr">
+      <c r="O58" t="n">
+        <v>50</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3871,7 +4223,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3881,47 +4233,53 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>XAI/KRW</t>
+          <t>SKL/KRW</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>17.35</v>
+        <v>10.34</v>
       </c>
       <c r="F59" t="n">
-        <v>17.6</v>
+        <v>10.34</v>
       </c>
       <c r="G59" t="n">
-        <v>1.440922190201729</v>
+        <v>10.34</v>
       </c>
       <c r="H59" t="n">
-        <v>15.66825</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>15.14122222222222</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>19.93156756756757</v>
+        <v>2.241191913449169</v>
       </c>
       <c r="K59" t="n">
+        <v>10.19055</v>
+      </c>
+      <c r="L59" t="n">
+        <v>9.967166666666666</v>
+      </c>
+      <c r="M59" t="n">
+        <v>13.24105945945946</v>
+      </c>
+      <c r="N59" t="n">
         <v>8</v>
       </c>
-      <c r="L59" t="n">
-        <v>50</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N59" t="n">
-        <v>2</v>
-      </c>
-      <c r="O59" t="inlineStr">
+      <c r="O59" t="n">
+        <v>50</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3930,7 +4288,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-14 00:18</t>
+          <t>2026-05-15 00:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3940,47 +4298,53 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BB/KRW</t>
+          <t>BEAM/KRW</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>47.49</v>
+        <v>2.863</v>
       </c>
       <c r="F60" t="n">
-        <v>47.49</v>
+        <v>2.863</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2.863</v>
       </c>
       <c r="H60" t="n">
-        <v>41.95825000000001</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>40.56533333333334</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>67.31308108108108</v>
+        <v>0.04460585689290841</v>
       </c>
       <c r="K60" t="n">
+        <v>2.897025</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2.895733333333333</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.731594594594595</v>
+      </c>
+      <c r="N60" t="n">
         <v>9</v>
       </c>
-      <c r="L60" t="n">
-        <v>50</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="inlineStr">
+      <c r="O60" t="n">
+        <v>50</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -3989,7 +4353,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3999,47 +4363,53 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ENA/KRW</t>
+          <t>STRK/KRW</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>174</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>174</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>158.325</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>155.7</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>241.9945945945946</v>
+        <v>0.4190568568462325</v>
       </c>
       <c r="K61" t="n">
+        <v>58.896</v>
+      </c>
+      <c r="L61" t="n">
+        <v>58.65022222222223</v>
+      </c>
+      <c r="M61" t="n">
+        <v>104.7097297297297</v>
+      </c>
+      <c r="N61" t="n">
         <v>10</v>
       </c>
-      <c r="L61" t="n">
-        <v>50</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N61" t="n">
-        <v>2</v>
-      </c>
-      <c r="O61" t="inlineStr">
+      <c r="O61" t="n">
+        <v>50</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4048,7 +4418,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4058,47 +4428,53 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MOCA/KRW</t>
+          <t>SC/KRW</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>21.79</v>
+        <v>1.453</v>
       </c>
       <c r="F62" t="n">
-        <v>21.39</v>
+        <v>1.453</v>
       </c>
       <c r="G62" t="n">
-        <v>-1.835704451583289</v>
+        <v>1.453</v>
       </c>
       <c r="H62" t="n">
-        <v>20.23025</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>21.15044444444444</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>27.54054054054054</v>
+        <v>4.806858041216471</v>
       </c>
       <c r="K62" t="n">
-        <v>8</v>
+        <v>1.4263</v>
       </c>
       <c r="L62" t="n">
-        <v>50</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>1.498322222222222</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.90654054054054</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O62" t="n">
+        <v>50</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4107,7 +4483,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4117,47 +4493,53 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TAIKO/KRW</t>
+          <t>AIOZ/KRW</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="F63" t="n">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="H63" t="n">
-        <v>174.5</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>178.1888888888889</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>220.9027027027027</v>
+        <v>0.4439766303190866</v>
       </c>
       <c r="K63" t="n">
-        <v>8</v>
+        <v>94.366</v>
       </c>
       <c r="L63" t="n">
-        <v>50</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>93.94888888888889</v>
+      </c>
+      <c r="M63" t="n">
+        <v>124.2780540540541</v>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
-      </c>
-      <c r="O63" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O63" t="n">
+        <v>50</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4166,7 +4548,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4176,47 +4558,53 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AVAIL/KRW</t>
+          <t>ArchLoot/KRW</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6.249</v>
+        <v>10.97</v>
       </c>
       <c r="F64" t="n">
-        <v>6.346</v>
+        <v>10.97</v>
       </c>
       <c r="G64" t="n">
-        <v>1.552248359737565</v>
+        <v>10.97</v>
       </c>
       <c r="H64" t="n">
-        <v>6.244</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>6.159077777777776</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>8.050886486486487</v>
+        <v>0.750298744204673</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>10.9886</v>
       </c>
       <c r="L64" t="n">
-        <v>50</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>10.90676666666667</v>
+      </c>
+      <c r="M64" t="n">
+        <v>14.6448054054054</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O64" t="n">
+        <v>50</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4225,7 +4613,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4235,47 +4623,53 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LISTA/KRW</t>
+          <t>BB/KRW</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>132</v>
+        <v>49.75</v>
       </c>
       <c r="F65" t="n">
-        <v>129</v>
+        <v>49.75</v>
       </c>
       <c r="G65" t="n">
-        <v>-2.272727272727273</v>
+        <v>49.75</v>
       </c>
       <c r="H65" t="n">
-        <v>128.2</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>127.7444444444444</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>186.0756756756757</v>
+        <v>4.347736833893983</v>
       </c>
       <c r="K65" t="n">
+        <v>42.3595</v>
+      </c>
+      <c r="L65" t="n">
+        <v>40.59455555555556</v>
+      </c>
+      <c r="M65" t="n">
+        <v>66.87221621621622</v>
+      </c>
+      <c r="N65" t="n">
         <v>9</v>
       </c>
-      <c r="L65" t="n">
-        <v>50</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="inlineStr">
+      <c r="O65" t="n">
+        <v>50</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4284,7 +4678,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4294,47 +4688,53 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EIGEN/KRW</t>
+          <t>ENA/KRW</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>315</v>
+        <v>180</v>
       </c>
       <c r="F66" t="n">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="G66" t="n">
-        <v>-1.26984126984127</v>
+        <v>180</v>
       </c>
       <c r="H66" t="n">
-        <v>270.65</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>275.6</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>463.6432432432433</v>
+        <v>2.786499215070652</v>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>160.05</v>
       </c>
       <c r="L66" t="n">
-        <v>50</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>155.7111111111111</v>
+      </c>
+      <c r="M66" t="n">
+        <v>240.3459459459459</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
-      </c>
-      <c r="O66" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O66" t="n">
+        <v>50</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4343,7 +4743,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4353,47 +4753,53 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ORDER/KRW</t>
+          <t>MOCA/KRW</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>83.59999999999999</v>
+        <v>22</v>
       </c>
       <c r="F67" t="n">
-        <v>82.98</v>
+        <v>22</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.7416267942583616</v>
+        <v>22</v>
       </c>
       <c r="H67" t="n">
-        <v>84.90025</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>82.37244444444444</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>113.8005945945946</v>
+        <v>3.816143238223511</v>
       </c>
       <c r="K67" t="n">
+        <v>20.312</v>
+      </c>
+      <c r="L67" t="n">
+        <v>21.11788888888889</v>
+      </c>
+      <c r="M67" t="n">
+        <v>27.32945945945946</v>
+      </c>
+      <c r="N67" t="n">
         <v>8</v>
       </c>
-      <c r="L67" t="n">
-        <v>50</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>2</v>
-      </c>
-      <c r="O67" t="inlineStr">
+      <c r="O67" t="n">
+        <v>50</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4402,7 +4808,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4412,47 +4818,53 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SCR/KRW</t>
+          <t>TAIKO/KRW</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>73.76000000000001</v>
+        <v>176</v>
       </c>
       <c r="F68" t="n">
-        <v>72.37</v>
+        <v>176</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.884490238611714</v>
+        <v>176</v>
       </c>
       <c r="H68" t="n">
-        <v>68.55549999999999</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>66.59966666666666</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>96.36064864864865</v>
+        <v>1.8881468073154</v>
       </c>
       <c r="K68" t="n">
-        <v>9</v>
+        <v>174.65</v>
       </c>
       <c r="L68" t="n">
-        <v>50</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>178.0111111111111</v>
+      </c>
+      <c r="M68" t="n">
+        <v>219.8864864864865</v>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
-      </c>
-      <c r="O68" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O68" t="n">
+        <v>50</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4461,7 +4873,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-14 00:19</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4471,47 +4883,53 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SWELL/KRW</t>
+          <t>AVAIL/KRW</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1.941</v>
+        <v>6.281</v>
       </c>
       <c r="F69" t="n">
-        <v>1.941</v>
+        <v>6.281</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>6.281</v>
       </c>
       <c r="H69" t="n">
-        <v>1.7952</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1.8297</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>2.408745945945946</v>
+        <v>1.051502571612002</v>
       </c>
       <c r="K69" t="n">
-        <v>10</v>
+        <v>6.226075</v>
       </c>
       <c r="L69" t="n">
-        <v>50</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>6.161288888888889</v>
+      </c>
+      <c r="M69" t="n">
+        <v>8.015140540540541</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
-      </c>
-      <c r="O69" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O69" t="n">
+        <v>50</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4520,7 +4938,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4530,47 +4948,53 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MVL/KRW</t>
+          <t>LISTA/KRW</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.956</v>
+        <v>130</v>
       </c>
       <c r="F70" t="n">
-        <v>1.941</v>
+        <v>130</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.7668711656441668</v>
+        <v>130</v>
       </c>
       <c r="H70" t="n">
-        <v>1.947125</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1.980655555555555</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>2.243783783783784</v>
+        <v>0.2851545494122699</v>
       </c>
       <c r="K70" t="n">
+        <v>127.975</v>
+      </c>
+      <c r="L70" t="n">
+        <v>127.6111111111111</v>
+      </c>
+      <c r="M70" t="n">
+        <v>184.6108108108108</v>
+      </c>
+      <c r="N70" t="n">
         <v>10</v>
       </c>
-      <c r="L70" t="n">
-        <v>50</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>2</v>
-      </c>
-      <c r="O70" t="inlineStr">
+      <c r="O70" t="n">
+        <v>50</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4579,7 +5003,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4589,47 +5013,53 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CARV/KRW</t>
+          <t>PEAQ/KRW</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>93.92</v>
+        <v>31.11</v>
       </c>
       <c r="F71" t="n">
-        <v>92.70999999999999</v>
+        <v>31.11</v>
       </c>
       <c r="G71" t="n">
-        <v>-1.288330494037487</v>
+        <v>31.11</v>
       </c>
       <c r="H71" t="n">
-        <v>86.4085</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>86.78100000000001</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>134.1495675675675</v>
+        <v>3.495689815503634</v>
       </c>
       <c r="K71" t="n">
-        <v>10</v>
+        <v>24.73225</v>
       </c>
       <c r="L71" t="n">
-        <v>50</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>23.89688888888889</v>
+      </c>
+      <c r="M71" t="n">
+        <v>37.46345945945946</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
-      </c>
-      <c r="O71" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O71" t="n">
+        <v>50</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4638,7 +5068,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4648,7 +5078,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>F/KRW</t>
+          <t>SCR/KRW</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4657,38 +5087,44 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8.49</v>
+        <v>75.03</v>
       </c>
       <c r="F72" t="n">
-        <v>8.407999999999999</v>
+        <v>75.03</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.9658421672556036</v>
+        <v>75.03</v>
       </c>
       <c r="H72" t="n">
-        <v>8.186575000000001</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>8.1966</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>9.694513513513515</v>
+        <v>3.422439551749498</v>
       </c>
       <c r="K72" t="n">
-        <v>9</v>
+        <v>68.87899999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>50</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>66.59966666666666</v>
+      </c>
+      <c r="M72" t="n">
+        <v>95.48524324324325</v>
       </c>
       <c r="N72" t="n">
-        <v>4</v>
-      </c>
-      <c r="O72" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O72" t="n">
+        <v>50</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4697,7 +5133,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4707,47 +5143,53 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ME/KRW</t>
+          <t>PONKE/KRW</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>167</v>
+        <v>50.03</v>
       </c>
       <c r="F73" t="n">
-        <v>164</v>
+        <v>50.03</v>
       </c>
       <c r="G73" t="n">
-        <v>-1.796407185628742</v>
+        <v>50.03</v>
       </c>
       <c r="H73" t="n">
-        <v>159.375</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>165.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>274.3891891891892</v>
+        <v>1.295429222429503</v>
       </c>
       <c r="K73" t="n">
+        <v>43.80125</v>
+      </c>
+      <c r="L73" t="n">
+        <v>44.37611111111111</v>
+      </c>
+      <c r="M73" t="n">
+        <v>50.9752972972973</v>
+      </c>
+      <c r="N73" t="n">
         <v>9</v>
       </c>
-      <c r="L73" t="n">
-        <v>50</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N73" t="n">
-        <v>1</v>
-      </c>
-      <c r="O73" t="inlineStr">
+      <c r="O73" t="n">
+        <v>50</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4756,7 +5198,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-14 08:02</t>
+          <t>2026-05-15 00:16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4766,47 +5208,53 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VANA/KRW</t>
+          <t>CARV/KRW</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2325</v>
+        <v>92.23</v>
       </c>
       <c r="F74" t="n">
-        <v>2298</v>
+        <v>92.23</v>
       </c>
       <c r="G74" t="n">
-        <v>-1.161290322580645</v>
+        <v>92.23</v>
       </c>
       <c r="H74" t="n">
-        <v>2141.525</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>2106.877777777778</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>2894.551351351352</v>
+        <v>0.2550258391141588</v>
       </c>
       <c r="K74" t="n">
+        <v>86.44775000000001</v>
+      </c>
+      <c r="L74" t="n">
+        <v>86.66877777777778</v>
+      </c>
+      <c r="M74" t="n">
+        <v>133.1976756756757</v>
+      </c>
+      <c r="N74" t="n">
         <v>10</v>
       </c>
-      <c r="L74" t="n">
-        <v>50</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>1</v>
-      </c>
-      <c r="O74" t="inlineStr">
+      <c r="O74" t="n">
+        <v>50</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4815,7 +5263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4825,7 +5273,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HP/KRW</t>
+          <t>F/KRW</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4834,38 +5282,44 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>23.94</v>
+        <v>8.465999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>23.52</v>
+        <v>8.465999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>-1.754385964912288</v>
+        <v>8.465999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>23.28975</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>24.34577777777778</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>29.51983783783784</v>
+        <v>0.3496304139770668</v>
       </c>
       <c r="K75" t="n">
-        <v>8</v>
+        <v>8.21345</v>
       </c>
       <c r="L75" t="n">
-        <v>50</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>8.184833333333334</v>
+      </c>
+      <c r="M75" t="n">
+        <v>9.643394594594595</v>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
-      </c>
-      <c r="O75" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O75" t="n">
+        <v>50</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4874,7 +5328,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:16</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4884,7 +5338,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GAME2/KRW</t>
+          <t>NIL/KRW</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4893,38 +5347,44 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2.052</v>
+        <v>79.63</v>
       </c>
       <c r="F76" t="n">
-        <v>2.042</v>
+        <v>79.63</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.487329434697867</v>
+        <v>79.63</v>
       </c>
       <c r="H76" t="n">
-        <v>2.03795</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2.058766666666667</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>2.305145945945946</v>
+        <v>3.397486680545797</v>
       </c>
       <c r="K76" t="n">
-        <v>9</v>
+        <v>64.086</v>
       </c>
       <c r="L76" t="n">
-        <v>50</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>66.33988888888888</v>
+      </c>
+      <c r="M76" t="n">
+        <v>93.86205405405406</v>
       </c>
       <c r="N76" t="n">
-        <v>3</v>
-      </c>
-      <c r="O76" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O76" t="n">
+        <v>50</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4933,7 +5393,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:16</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4943,47 +5403,53 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ERA/KRW</t>
+          <t>BLUE/KRW</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>209</v>
+        <v>27.79</v>
       </c>
       <c r="F77" t="n">
-        <v>205</v>
+        <v>27.79</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.913875598086124</v>
+        <v>27.79</v>
       </c>
       <c r="H77" t="n">
-        <v>202.925</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>205.4555555555555</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>261.9837837837838</v>
+        <v>2.857036012116237</v>
       </c>
       <c r="K77" t="n">
-        <v>9</v>
+        <v>25.977</v>
       </c>
       <c r="L77" t="n">
-        <v>50</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>26.741</v>
+      </c>
+      <c r="M77" t="n">
+        <v>40.39627027027027</v>
       </c>
       <c r="N77" t="n">
-        <v>2</v>
-      </c>
-      <c r="O77" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O77" t="n">
+        <v>50</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -4992,7 +5458,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5002,47 +5468,53 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>COOKIE/KRW</t>
+          <t>GAME2/KRW</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>26.37</v>
+        <v>2.064</v>
       </c>
       <c r="F78" t="n">
-        <v>26.06</v>
+        <v>2.064</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.175578308684119</v>
+        <v>2.064</v>
       </c>
       <c r="H78" t="n">
-        <v>25.3865</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>26.18388888888889</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>44.86248648648648</v>
+        <v>1.002962747097957</v>
       </c>
       <c r="K78" t="n">
-        <v>10</v>
+        <v>2.03825</v>
       </c>
       <c r="L78" t="n">
-        <v>50</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>2.0589</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2.305210810810811</v>
       </c>
       <c r="N78" t="n">
-        <v>2</v>
-      </c>
-      <c r="O78" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O78" t="n">
+        <v>50</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5051,7 +5523,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5061,47 +5533,53 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ANIME/KRW</t>
+          <t>ERA/KRW</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>7.055</v>
+        <v>206</v>
       </c>
       <c r="F79" t="n">
-        <v>7.019</v>
+        <v>206</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.5102763997165073</v>
+        <v>206</v>
       </c>
       <c r="H79" t="n">
-        <v>7.043049999999999</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>7.137644444444445</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>8.645200000000001</v>
+        <v>0.7980597257601257</v>
       </c>
       <c r="K79" t="n">
-        <v>10</v>
+        <v>203.375</v>
       </c>
       <c r="L79" t="n">
-        <v>50</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>205.0111111111111</v>
+      </c>
+      <c r="M79" t="n">
+        <v>261.0702702702703</v>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
-      </c>
-      <c r="O79" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O79" t="n">
+        <v>50</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5110,7 +5588,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5120,47 +5598,53 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>WCT/KRW</t>
+          <t>COOKIE/KRW</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>98.33</v>
+        <v>26.55</v>
       </c>
       <c r="F80" t="n">
-        <v>95.78</v>
+        <v>26.55</v>
       </c>
       <c r="G80" t="n">
-        <v>-2.593308247737208</v>
+        <v>26.55</v>
       </c>
       <c r="H80" t="n">
-        <v>91.84125</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>89.79055555555556</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>109.4678378378378</v>
+        <v>2.687664911855825</v>
       </c>
       <c r="K80" t="n">
-        <v>8</v>
+        <v>25.4475</v>
       </c>
       <c r="L80" t="n">
-        <v>50</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>26.15033333333334</v>
+      </c>
+      <c r="M80" t="n">
+        <v>44.41237837837837</v>
       </c>
       <c r="N80" t="n">
-        <v>2</v>
-      </c>
-      <c r="O80" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O80" t="n">
+        <v>50</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5169,7 +5653,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5179,47 +5663,53 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FLOCK/KRW</t>
+          <t>LAYER/KRW</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>94.20999999999999</v>
+        <v>148</v>
       </c>
       <c r="F81" t="n">
-        <v>93.09999999999999</v>
+        <v>148</v>
       </c>
       <c r="G81" t="n">
-        <v>-1.178218872731132</v>
+        <v>148</v>
       </c>
       <c r="H81" t="n">
-        <v>91.60499999999999</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>88.01377777777778</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>120.3695675675676</v>
+        <v>3.073394495412831</v>
       </c>
       <c r="K81" t="n">
+        <v>131.075</v>
+      </c>
+      <c r="L81" t="n">
+        <v>127.1666666666667</v>
+      </c>
+      <c r="M81" t="n">
+        <v>191.1675675675676</v>
+      </c>
+      <c r="N81" t="n">
         <v>9</v>
       </c>
-      <c r="L81" t="n">
-        <v>50</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="inlineStr">
+      <c r="O81" t="n">
+        <v>50</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5228,7 +5718,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5238,47 +5728,53 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMT/KRW</t>
+          <t>WCT/KRW</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>25.94</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="F82" t="n">
-        <v>26.14</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>0.771010023130298</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>23.66975</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>23.34233333333333</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>30.09567567567568</v>
+        <v>2.693916975640177</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>92.20225000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>50</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>89.78355555555557</v>
+      </c>
+      <c r="M82" t="n">
+        <v>108.9808648648649</v>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O82" t="n">
+        <v>50</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5287,7 +5783,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-14 00:20</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5297,47 +5793,53 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>XTER/KRW</t>
+          <t>FLOCK/KRW</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>27.64</v>
+        <v>93.37</v>
       </c>
       <c r="F83" t="n">
-        <v>27.64</v>
+        <v>93.37</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>93.37</v>
       </c>
       <c r="H83" t="n">
-        <v>25.858</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>25.50722222222222</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>38.81918918918919</v>
+        <v>4.588487293283801</v>
       </c>
       <c r="K83" t="n">
+        <v>92.01300000000001</v>
+      </c>
+      <c r="L83" t="n">
+        <v>87.97622222222222</v>
+      </c>
+      <c r="M83" t="n">
+        <v>119.2817837837838</v>
+      </c>
+      <c r="N83" t="n">
         <v>8</v>
       </c>
-      <c r="L83" t="n">
-        <v>50</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N83" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" t="inlineStr">
+      <c r="O83" t="n">
+        <v>50</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5346,7 +5848,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5356,47 +5858,53 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0G/KRW</t>
+          <t>BMT/KRW</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>813</v>
+        <v>26.1</v>
       </c>
       <c r="F84" t="n">
-        <v>810</v>
+        <v>26.1</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.3690036900369004</v>
+        <v>26.1</v>
       </c>
       <c r="H84" t="n">
-        <v>826.575</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>841.5333333333333</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1126.443243243243</v>
+        <v>1.848180970149254</v>
       </c>
       <c r="K84" t="n">
-        <v>10</v>
+        <v>23.77725</v>
       </c>
       <c r="L84" t="n">
-        <v>50</v>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>23.34577777777778</v>
+      </c>
+      <c r="M84" t="n">
+        <v>29.95291891891892</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
-      </c>
-      <c r="O84" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O84" t="n">
+        <v>50</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5405,7 +5913,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-14 08:04</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5415,47 +5923,53 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HEMI/KRW</t>
+          <t>WAL/KRW</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>12.42</v>
+        <v>122</v>
       </c>
       <c r="F85" t="n">
-        <v>12.14</v>
+        <v>122</v>
       </c>
       <c r="G85" t="n">
-        <v>-2.254428341384858</v>
+        <v>122</v>
       </c>
       <c r="H85" t="n">
-        <v>11.731</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>11.81388888888889</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>18.45291891891892</v>
+        <v>1.875942572823033</v>
       </c>
       <c r="K85" t="n">
-        <v>9</v>
+        <v>110.175</v>
       </c>
       <c r="L85" t="n">
-        <v>48</v>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>112.2813333333333</v>
+      </c>
+      <c r="M85" t="n">
+        <v>158.9152432432433</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
-      </c>
-      <c r="O85" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O85" t="n">
+        <v>50</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5464,7 +5978,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-14 08:04</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5474,47 +5988,53 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SOPH/KRW</t>
+          <t>XTER/KRW</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>13.41</v>
+        <v>26.16</v>
       </c>
       <c r="F86" t="n">
-        <v>13.09</v>
+        <v>26.16</v>
       </c>
       <c r="G86" t="n">
-        <v>-2.386278896346013</v>
+        <v>26.16</v>
       </c>
       <c r="H86" t="n">
-        <v>13.03675</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>13.08855555555556</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>17.00908108108108</v>
+        <v>1.154922394968436</v>
       </c>
       <c r="K86" t="n">
-        <v>10</v>
+        <v>25.78675</v>
       </c>
       <c r="L86" t="n">
-        <v>50</v>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>25.49233333333333</v>
+      </c>
+      <c r="M86" t="n">
+        <v>38.49189189189189</v>
       </c>
       <c r="N86" t="n">
-        <v>2</v>
-      </c>
-      <c r="O86" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O86" t="n">
+        <v>50</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5523,7 +6043,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-14 08:04</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5533,47 +6053,53 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TREE/KRW</t>
+          <t>0G/KRW</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103</v>
+        <v>813</v>
       </c>
       <c r="F87" t="n">
-        <v>103</v>
+        <v>813</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>813</v>
       </c>
       <c r="H87" t="n">
-        <v>100.36225</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>99.54544444444444</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>132.405027027027</v>
+        <v>1.455402475142803</v>
       </c>
       <c r="K87" t="n">
+        <v>828.125</v>
+      </c>
+      <c r="L87" t="n">
+        <v>840.3555555555556</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1119.983783783784</v>
+      </c>
+      <c r="N87" t="n">
         <v>10</v>
       </c>
-      <c r="L87" t="n">
-        <v>50</v>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N87" t="n">
-        <v>2</v>
-      </c>
-      <c r="O87" t="inlineStr">
+      <c r="O87" t="n">
+        <v>50</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5582,7 +6108,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-14 08:04</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5592,47 +6118,53 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PUMP/KRW</t>
+          <t>KMNO/KRW</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.8</v>
+        <v>34.14</v>
       </c>
       <c r="F88" t="n">
-        <v>2.753</v>
+        <v>34.14</v>
       </c>
       <c r="G88" t="n">
-        <v>-1.678571428571418</v>
+        <v>34.14</v>
       </c>
       <c r="H88" t="n">
-        <v>2.757525</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>2.799388888888889</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>3.321751351351351</v>
+        <v>1.899789812713734</v>
       </c>
       <c r="K88" t="n">
-        <v>8</v>
+        <v>31.27075</v>
       </c>
       <c r="L88" t="n">
-        <v>50</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>31.87633333333334</v>
+      </c>
+      <c r="M88" t="n">
+        <v>54.82308108108109</v>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O88" t="n">
+        <v>50</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5641,7 +6173,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-14 08:04</t>
+          <t>2026-05-15 00:17</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5651,47 +6183,53 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MIRA/KRW</t>
+          <t>HEMI/KRW</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>124</v>
+        <v>12.53</v>
       </c>
       <c r="F89" t="n">
-        <v>123</v>
+        <v>12.53</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.8064516129032258</v>
+        <v>12.53</v>
       </c>
       <c r="H89" t="n">
-        <v>123.425</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>123.4777777777778</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>166.7675675675676</v>
+        <v>0.2317259457624554</v>
       </c>
       <c r="K89" t="n">
-        <v>10</v>
+        <v>11.75625</v>
       </c>
       <c r="L89" t="n">
-        <v>46</v>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>11.78355555555556</v>
+      </c>
+      <c r="M89" t="n">
+        <v>18.24275675675676</v>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
-      </c>
-      <c r="O89" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O89" t="n">
+        <v>49</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5700,7 +6238,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-14 08:04</t>
+          <t>2026-05-15 00:18</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5710,47 +6248,53 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LINEA/KRW</t>
+          <t>SOPH/KRW</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5.659</v>
+        <v>13.25</v>
       </c>
       <c r="F90" t="n">
-        <v>5.696</v>
+        <v>13.25</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6538257642693042</v>
+        <v>13.25</v>
       </c>
       <c r="H90" t="n">
-        <v>5.222625</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>4.986977777777778</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>7.904821621621622</v>
+        <v>0.07907154699655805</v>
       </c>
       <c r="K90" t="n">
-        <v>8</v>
+        <v>13.058</v>
       </c>
       <c r="L90" t="n">
-        <v>50</v>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>13.06833333333333</v>
+      </c>
+      <c r="M90" t="n">
+        <v>16.89778378378378</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
-      </c>
-      <c r="O90" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O90" t="n">
+        <v>50</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5759,7 +6303,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-14 08:04</t>
+          <t>2026-05-15 00:18</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5769,47 +6313,53 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ZKC/KRW</t>
+          <t>TREE/KRW</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F91" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G91" t="n">
-        <v>-1.754385964912281</v>
+        <v>105</v>
       </c>
       <c r="H91" t="n">
-        <v>110.2</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>115.8666666666667</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>150.2756756756757</v>
+        <v>1.42315928459164</v>
       </c>
       <c r="K91" t="n">
-        <v>8</v>
+        <v>100.88325</v>
       </c>
       <c r="L91" t="n">
-        <v>50</v>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>99.46766666666667</v>
+      </c>
+      <c r="M91" t="n">
+        <v>131.7293513513513</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="O91" t="n">
+        <v>50</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5818,7 +6368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-14 08:04</t>
+          <t>2026-05-15 00:18</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5828,47 +6378,53 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SUPER/KRW</t>
+          <t>AVNT/KRW</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="F92" t="n">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="G92" t="n">
-        <v>-1.595744680851064</v>
+        <v>227</v>
       </c>
       <c r="H92" t="n">
-        <v>182.6</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>175.3222222222222</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>248.1351351351351</v>
+        <v>4.943820224719111</v>
       </c>
       <c r="K92" t="n">
-        <v>8</v>
+        <v>216.2</v>
       </c>
       <c r="L92" t="n">
-        <v>40</v>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>227.4444444444445</v>
+      </c>
+      <c r="M92" t="n">
+        <v>354.4162162162162</v>
       </c>
       <c r="N92" t="n">
-        <v>2</v>
-      </c>
-      <c r="O92" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O92" t="n">
+        <v>50</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5877,7 +6433,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-14 00:26</t>
+          <t>2026-05-15 00:18</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5887,47 +6443,53 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CRO/KRW</t>
+          <t>PUMP/KRW</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>113</v>
+        <v>2.83</v>
       </c>
       <c r="F93" t="n">
-        <v>113</v>
+        <v>2.83</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="H93" t="n">
-        <v>104.975</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>108.8111111111111</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>127.3945945945946</v>
+        <v>1.039559496226472</v>
       </c>
       <c r="K93" t="n">
-        <v>9</v>
+        <v>2.766725</v>
       </c>
       <c r="L93" t="n">
-        <v>50</v>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>2.795788888888889</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3.301189189189189</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="O93" t="n">
+        <v>50</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5936,7 +6498,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-14 00:28</t>
+          <t>2026-05-15 00:18</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5946,47 +6508,53 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IMX/KRW</t>
+          <t>SD/KRW</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="F94" t="n">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="H94" t="n">
-        <v>245.425</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>239.1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>318.8648648648648</v>
+        <v>0.7136022962844877</v>
       </c>
       <c r="K94" t="n">
-        <v>9</v>
+        <v>210.525</v>
       </c>
       <c r="L94" t="n">
-        <v>50</v>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
+        <v>209.0333333333333</v>
+      </c>
+      <c r="M94" t="n">
+        <v>285.2054054054054</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
-      </c>
-      <c r="O94" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="O94" t="n">
+        <v>50</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -5995,7 +6563,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-14 00:30</t>
+          <t>2026-05-15 00:18</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6005,47 +6573,53 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>STRAX/KRW</t>
+          <t>MIRA/KRW</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>19.89</v>
+        <v>122</v>
       </c>
       <c r="F95" t="n">
-        <v>19.89</v>
+        <v>122</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H95" t="n">
-        <v>19.633</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>20.43911111111111</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>26.33864864864865</v>
+        <v>0.2613789995493471</v>
       </c>
       <c r="K95" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="L95" t="n">
+        <v>123.2777777777778</v>
+      </c>
+      <c r="M95" t="n">
+        <v>165.6810810810811</v>
+      </c>
+      <c r="N95" t="n">
         <v>10</v>
       </c>
-      <c r="L95" t="n">
-        <v>50</v>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N95" t="n">
-        <v>1</v>
-      </c>
-      <c r="O95" t="inlineStr">
+      <c r="O95" t="n">
+        <v>47</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -6054,7 +6628,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-14 00:49</t>
+          <t>2026-05-15 00:18</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6064,7 +6638,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EL/KRW</t>
+          <t>XAN/KRW</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6073,38 +6647,44 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2.871</v>
+        <v>15.02</v>
       </c>
       <c r="F96" t="n">
-        <v>2.871</v>
+        <v>15.02</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>15.02</v>
       </c>
       <c r="H96" t="n">
-        <v>2.77225</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>2.822322222222222</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>3.123027027027027</v>
+        <v>2.664253498944049</v>
       </c>
       <c r="K96" t="n">
+        <v>12.74725</v>
+      </c>
+      <c r="L96" t="n">
+        <v>12.41644444444444</v>
+      </c>
+      <c r="M96" t="n">
+        <v>19.85772972972973</v>
+      </c>
+      <c r="N96" t="n">
         <v>8</v>
       </c>
-      <c r="L96" t="n">
-        <v>50</v>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N96" t="n">
-        <v>3</v>
-      </c>
-      <c r="O96" t="inlineStr">
+      <c r="O96" t="n">
+        <v>36</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -6113,7 +6693,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-14 08:01</t>
+          <t>2026-05-15 00:18</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6123,47 +6703,53 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TT/KRW</t>
+          <t>ZKC/KRW</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.332</v>
+        <v>113</v>
       </c>
       <c r="F97" t="n">
-        <v>1.332</v>
+        <v>113</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="H97" t="n">
-        <v>1.32475</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>1.315277777777778</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>1.513091891891892</v>
+        <v>4.360381172393876</v>
       </c>
       <c r="K97" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="L97" t="n">
+        <v>115.4333333333333</v>
+      </c>
+      <c r="M97" t="n">
+        <v>149.3081081081081</v>
+      </c>
+      <c r="N97" t="n">
         <v>9</v>
       </c>
-      <c r="L97" t="n">
-        <v>50</v>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N97" t="n">
-        <v>1</v>
-      </c>
-      <c r="O97" t="inlineStr">
+      <c r="O97" t="n">
+        <v>50</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
@@ -6172,7 +6758,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-14 08:03</t>
+          <t>2026-05-15 00:18</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6182,47 +6768,443 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>QKC/KRW</t>
+          <t>SUPER/KRW</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>188</v>
+      </c>
+      <c r="F98" t="n">
+        <v>188</v>
+      </c>
+      <c r="G98" t="n">
+        <v>188</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>4.811715481171533</v>
+      </c>
+      <c r="K98" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="L98" t="n">
+        <v>175.2666666666667</v>
+      </c>
+      <c r="M98" t="n">
+        <v>246.6216216216216</v>
+      </c>
+      <c r="N98" t="n">
+        <v>8</v>
+      </c>
+      <c r="O98" t="n">
+        <v>41</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:23</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ADA/KRW</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>400</v>
+      </c>
+      <c r="F99" t="n">
+        <v>400</v>
+      </c>
+      <c r="G99" t="n">
+        <v>400</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>2.291995976433389</v>
+      </c>
+      <c r="K99" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="L99" t="n">
+        <v>386.6111111111111</v>
+      </c>
+      <c r="M99" t="n">
+        <v>479.1189189189189</v>
+      </c>
+      <c r="N99" t="n">
+        <v>10</v>
+      </c>
+      <c r="O99" t="n">
+        <v>50</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:25</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>GALA/KRW</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="F100" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="G100" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.9143501576867312</v>
+      </c>
+      <c r="K100" t="n">
+        <v>4.964125</v>
+      </c>
+      <c r="L100" t="n">
+        <v>5.009933333333334</v>
+      </c>
+      <c r="M100" t="n">
+        <v>7.510124324324323</v>
+      </c>
+      <c r="N100" t="n">
+        <v>9</v>
+      </c>
+      <c r="O100" t="n">
+        <v>50</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:25</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>XCN/KRW</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="F101" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="G101" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.5405673699577851</v>
+      </c>
+      <c r="K101" t="n">
+        <v>7.403075000000001</v>
+      </c>
+      <c r="L101" t="n">
+        <v>7.44331111111111</v>
+      </c>
+      <c r="M101" t="n">
+        <v>8.124902702702702</v>
+      </c>
+      <c r="N101" t="n">
+        <v>8</v>
+      </c>
+      <c r="O101" t="n">
+        <v>50</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:36</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SWELL/KRW</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>S+</t>
         </is>
       </c>
-      <c r="E98" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F98" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>4.6238</v>
-      </c>
-      <c r="I98" t="n">
-        <v>4.669788888888889</v>
-      </c>
-      <c r="J98" t="n">
-        <v>5.402454054054054</v>
-      </c>
-      <c r="K98" t="n">
+      <c r="E102" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1.766487418215367</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1.79835</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1.830688888888889</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2.388151351351351</v>
+      </c>
+      <c r="N102" t="n">
+        <v>10</v>
+      </c>
+      <c r="O102" t="n">
+        <v>50</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:37</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>WIF/KRW</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>326</v>
+      </c>
+      <c r="F103" t="n">
+        <v>326</v>
+      </c>
+      <c r="G103" t="n">
+        <v>326</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2.033373109049605</v>
+      </c>
+      <c r="K103" t="n">
+        <v>294.525</v>
+      </c>
+      <c r="L103" t="n">
+        <v>288.6555555555556</v>
+      </c>
+      <c r="M103" t="n">
+        <v>402.2972972972973</v>
+      </c>
+      <c r="N103" t="n">
+        <v>8</v>
+      </c>
+      <c r="O103" t="n">
+        <v>50</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:47</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AZIT/KRW</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6.394</v>
+      </c>
+      <c r="F104" t="n">
+        <v>6.394</v>
+      </c>
+      <c r="G104" t="n">
+        <v>6.394</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.1087952996719093</v>
+      </c>
+      <c r="K104" t="n">
+        <v>5.980775</v>
+      </c>
+      <c r="L104" t="n">
+        <v>5.987288888888889</v>
+      </c>
+      <c r="M104" t="n">
+        <v>7.954832432432433</v>
+      </c>
+      <c r="N104" t="n">
         <v>9</v>
       </c>
-      <c r="L98" t="n">
-        <v>50</v>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>90_Touch</t>
-        </is>
-      </c>
-      <c r="N98" t="n">
-        <v>1</v>
-      </c>
-      <c r="O98" t="inlineStr">
+      <c r="O104" t="n">
+        <v>50</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>

--- a/trades/rise_strategy_tracking_v1.xlsx
+++ b/trades/rise_strategy_tracking_v1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:Q142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -540,13 +540,13 @@
         <v>118</v>
       </c>
       <c r="F2" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G2" t="n">
         <v>118</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-3.389830508474576</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -583,7 +583,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -605,16 +605,16 @@
         <v>81.48999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>81.48999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>81.48999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2.552460424591973</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2.589274757638973</v>
       </c>
       <c r="J3" t="n">
         <v>2.303834876427843</v>
@@ -648,7 +648,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00</t>
+          <t>2026-05-15 14:02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -670,16 +670,16 @@
         <v>13.05</v>
       </c>
       <c r="F4" t="n">
-        <v>13.05</v>
+        <v>13.46</v>
       </c>
       <c r="G4" t="n">
-        <v>13.05</v>
+        <v>13.46</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3.141762452107281</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3.141762452107281</v>
       </c>
       <c r="J4" t="n">
         <v>0.1836402984940497</v>
@@ -713,7 +713,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -735,13 +735,13 @@
         <v>381</v>
       </c>
       <c r="F5" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G5" t="n">
         <v>381</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0.7874015748031495</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -800,13 +800,13 @@
         <v>496</v>
       </c>
       <c r="F6" t="n">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="G6" t="n">
         <v>496</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-2.419354838709677</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -865,13 +865,13 @@
         <v>143</v>
       </c>
       <c r="F7" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G7" t="n">
         <v>143</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-2.097902097902098</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00</t>
+          <t>2026-05-15 21:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -930,13 +930,13 @@
         <v>3301</v>
       </c>
       <c r="F8" t="n">
-        <v>3301</v>
+        <v>3225</v>
       </c>
       <c r="G8" t="n">
         <v>3301</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-2.302332626476825</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1103,7 +1103,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-15 00:02</t>
+          <t>2026-05-15 21:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1125,13 +1125,13 @@
         <v>13.8</v>
       </c>
       <c r="F11" t="n">
-        <v>13.8</v>
+        <v>13.58</v>
       </c>
       <c r="G11" t="n">
         <v>13.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.594202898550729</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-15 00:02</t>
+          <t>2026-05-15 21:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1190,13 +1190,13 @@
         <v>141</v>
       </c>
       <c r="F12" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G12" t="n">
         <v>141</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-2.127659574468085</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-15 00:02</t>
+          <t>2026-05-15 21:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1255,16 +1255,16 @@
         <v>14.51</v>
       </c>
       <c r="F13" t="n">
-        <v>14.51</v>
+        <v>14.31</v>
       </c>
       <c r="G13" t="n">
-        <v>14.51</v>
+        <v>14.66</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-1.37835975189524</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.033769813921436</v>
       </c>
       <c r="J13" t="n">
         <v>0.2703342596761479</v>
@@ -1298,7 +1298,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-15 00:03</t>
+          <t>2026-05-15 21:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1320,13 +1320,13 @@
         <v>560</v>
       </c>
       <c r="F14" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G14" t="n">
         <v>560</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-1.785714285714286</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-15 00:03</t>
+          <t>2026-05-15 21:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1450,13 +1450,13 @@
         <v>3026</v>
       </c>
       <c r="F16" t="n">
-        <v>3026</v>
+        <v>2972</v>
       </c>
       <c r="G16" t="n">
         <v>3026</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-1.784534038334435</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1493,7 +1493,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-15 00:03</t>
+          <t>2026-05-15 21:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1515,13 +1515,13 @@
         <v>8090</v>
       </c>
       <c r="F17" t="n">
-        <v>8090</v>
+        <v>7820</v>
       </c>
       <c r="G17" t="n">
         <v>8090</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-3.337453646477132</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-15 00:03</t>
+          <t>2026-05-15 21:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1580,13 +1580,13 @@
         <v>6495</v>
       </c>
       <c r="F18" t="n">
-        <v>6495</v>
+        <v>6355</v>
       </c>
       <c r="G18" t="n">
         <v>6495</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-2.155504234026174</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-15 00:03</t>
+          <t>2026-05-15 21:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1645,13 +1645,13 @@
         <v>3.212</v>
       </c>
       <c r="F19" t="n">
-        <v>3.212</v>
+        <v>3.165</v>
       </c>
       <c r="G19" t="n">
         <v>3.212</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-1.463262764632632</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-15 00:04</t>
+          <t>2026-05-15 21:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1710,16 +1710,16 @@
         <v>146</v>
       </c>
       <c r="F20" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G20" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-0.684931506849315</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="J20" t="n">
         <v>1.183009130607371</v>
@@ -1753,7 +1753,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-15 00:04</t>
+          <t>2026-05-15 21:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1775,13 +1775,13 @@
         <v>97.13</v>
       </c>
       <c r="F21" t="n">
-        <v>97.13</v>
+        <v>94.41</v>
       </c>
       <c r="G21" t="n">
         <v>97.13</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-2.800370637290229</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-15 00:06</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1840,16 +1840,16 @@
         <v>2169</v>
       </c>
       <c r="F22" t="n">
-        <v>2169</v>
+        <v>2174</v>
       </c>
       <c r="G22" t="n">
-        <v>2169</v>
+        <v>2181</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.2305209774089442</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.5532503457814661</v>
       </c>
       <c r="J22" t="n">
         <v>0.3286793868581832</v>
@@ -1948,7 +1948,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-15 00:06</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,7 +2013,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-15 00:06</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2035,16 +2035,16 @@
         <v>210</v>
       </c>
       <c r="F25" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G25" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="J25" t="n">
         <v>2.220197955188159</v>
@@ -2078,7 +2078,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-15 00:06</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2100,13 +2100,13 @@
         <v>6.236</v>
       </c>
       <c r="F26" t="n">
-        <v>6.236</v>
+        <v>6.069</v>
       </c>
       <c r="G26" t="n">
         <v>6.236</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>-2.67799871712636</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-15 00:06</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2165,16 +2165,16 @@
         <v>97</v>
       </c>
       <c r="F27" t="n">
-        <v>97</v>
+        <v>97.63</v>
       </c>
       <c r="G27" t="n">
-        <v>97</v>
+        <v>99.72</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.6494845360824696</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2.804123711340205</v>
       </c>
       <c r="J27" t="n">
         <v>1.652994214651095</v>
@@ -2208,7 +2208,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-15 00:09</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2230,13 +2230,13 @@
         <v>15.34</v>
       </c>
       <c r="F28" t="n">
-        <v>15.34</v>
+        <v>15.09</v>
       </c>
       <c r="G28" t="n">
         <v>15.34</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-1.629726205997392</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-15 00:09</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2295,13 +2295,13 @@
         <v>155</v>
       </c>
       <c r="F29" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G29" t="n">
         <v>155</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-0.6451612903225806</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2338,7 +2338,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-15 00:09</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2360,16 +2360,16 @@
         <v>47.5</v>
       </c>
       <c r="F30" t="n">
-        <v>47.5</v>
+        <v>46.85</v>
       </c>
       <c r="G30" t="n">
-        <v>47.5</v>
+        <v>49.33</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-1.368421052631576</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>3.852631578947365</v>
       </c>
       <c r="J30" t="n">
         <v>0.01688626856887497</v>
@@ -2403,7 +2403,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-15 00:09</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2425,13 +2425,13 @@
         <v>10.97</v>
       </c>
       <c r="F31" t="n">
-        <v>10.97</v>
+        <v>10.67</v>
       </c>
       <c r="G31" t="n">
         <v>10.97</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-2.73473108477667</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-15 00:10</t>
+          <t>2026-05-15 21:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2490,16 +2490,16 @@
         <v>112</v>
       </c>
       <c r="F32" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G32" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-0.8928571428571428</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="J32" t="n">
         <v>3.321749795584631</v>
@@ -2533,7 +2533,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-15 00:10</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2555,13 +2555,13 @@
         <v>1.424</v>
       </c>
       <c r="F33" t="n">
-        <v>1.424</v>
+        <v>1.398</v>
       </c>
       <c r="G33" t="n">
         <v>1.424</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>-1.825842696629215</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-15 00:10</t>
+          <t>2026-05-15 21:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2620,13 +2620,13 @@
         <v>2.85</v>
       </c>
       <c r="F34" t="n">
-        <v>2.85</v>
+        <v>2.835</v>
       </c>
       <c r="G34" t="n">
         <v>2.85</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-0.5263157894736885</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-15 00:10</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2685,13 +2685,13 @@
         <v>95.11</v>
       </c>
       <c r="F35" t="n">
-        <v>95.11</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>95.11</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-2.964987908737244</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2728,7 +2728,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-15 00:10</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2750,13 +2750,13 @@
         <v>2.403</v>
       </c>
       <c r="F36" t="n">
-        <v>2.403</v>
+        <v>2.309</v>
       </c>
       <c r="G36" t="n">
         <v>2.403</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-3.911776945484805</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-15 00:10</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2815,13 +2815,13 @@
         <v>732</v>
       </c>
       <c r="F37" t="n">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="G37" t="n">
         <v>732</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-0.9562841530054645</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-15 00:10</t>
+          <t>2026-05-15 21:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2880,13 +2880,13 @@
         <v>9.590999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>9.590999999999999</v>
+        <v>9.388999999999999</v>
       </c>
       <c r="G38" t="n">
         <v>9.590999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>-2.106141174017308</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-15 00:11</t>
+          <t>2026-05-15 14:03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2945,13 +2945,13 @@
         <v>11.63</v>
       </c>
       <c r="F39" t="n">
-        <v>11.63</v>
+        <v>11.38</v>
       </c>
       <c r="G39" t="n">
         <v>11.63</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-2.149613069647463</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2988,7 +2988,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-15 00:12</t>
+          <t>2026-05-15 21:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3010,13 +3010,13 @@
         <v>9.638999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>9.638999999999999</v>
+        <v>9.474</v>
       </c>
       <c r="G40" t="n">
         <v>9.638999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-1.71179582944288</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-15 00:12</t>
+          <t>2026-05-15 21:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3075,13 +3075,13 @@
         <v>4.338</v>
       </c>
       <c r="F41" t="n">
-        <v>4.338</v>
+        <v>4.336</v>
       </c>
       <c r="G41" t="n">
         <v>4.338</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-0.04610419548178376</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-15 00:12</t>
+          <t>2026-05-15 21:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3140,13 +3140,13 @@
         <v>2.101</v>
       </c>
       <c r="F42" t="n">
-        <v>2.101</v>
+        <v>2.071</v>
       </c>
       <c r="G42" t="n">
         <v>2.101</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-1.427891480247492</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-15 00:12</t>
+          <t>2026-05-15 21:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3205,13 +3205,13 @@
         <v>9.02</v>
       </c>
       <c r="F43" t="n">
-        <v>9.02</v>
+        <v>8.879</v>
       </c>
       <c r="G43" t="n">
         <v>9.02</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-1.563192904656319</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-15 00:12</t>
+          <t>2026-05-15 21:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3270,13 +3270,13 @@
         <v>61.21</v>
       </c>
       <c r="F44" t="n">
-        <v>61.21</v>
+        <v>60.51</v>
       </c>
       <c r="G44" t="n">
         <v>61.21</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-1.143603986276757</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-15 00:12</t>
+          <t>2026-05-15 21:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3335,13 +3335,13 @@
         <v>18.28</v>
       </c>
       <c r="F45" t="n">
-        <v>18.28</v>
+        <v>18.06</v>
       </c>
       <c r="G45" t="n">
         <v>18.28</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-1.203501094091917</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -3378,7 +3378,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-15 00:12</t>
+          <t>2026-05-15 21:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3400,16 +3400,16 @@
         <v>53.89</v>
       </c>
       <c r="F46" t="n">
-        <v>53.89</v>
+        <v>54.46</v>
       </c>
       <c r="G46" t="n">
-        <v>53.89</v>
+        <v>54.46</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1.05771015030618</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1.05771015030618</v>
       </c>
       <c r="J46" t="n">
         <v>0.7622745586497198</v>
@@ -3443,7 +3443,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-15 00:13</t>
+          <t>2026-05-15 21:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3465,13 +3465,13 @@
         <v>6.594</v>
       </c>
       <c r="F47" t="n">
-        <v>6.594</v>
+        <v>6.573</v>
       </c>
       <c r="G47" t="n">
         <v>6.594</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-0.3184713375796164</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-15 00:13</t>
+          <t>2026-05-15 21:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3530,16 +3530,16 @@
         <v>2.315</v>
       </c>
       <c r="F48" t="n">
-        <v>2.315</v>
+        <v>2.33</v>
       </c>
       <c r="G48" t="n">
-        <v>2.315</v>
+        <v>2.33</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>0.6479481641468736</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>0.6479481641468736</v>
       </c>
       <c r="J48" t="n">
         <v>0.0008501583723555123</v>
@@ -3573,7 +3573,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-15 00:13</t>
+          <t>2026-05-15 21:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3595,13 +3595,13 @@
         <v>22.95</v>
       </c>
       <c r="F49" t="n">
-        <v>22.95</v>
+        <v>22.34</v>
       </c>
       <c r="G49" t="n">
         <v>22.95</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>-2.657952069716773</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-15 00:13</t>
+          <t>2026-05-15 21:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3660,13 +3660,13 @@
         <v>73.61</v>
       </c>
       <c r="F50" t="n">
-        <v>73.61</v>
+        <v>71.83</v>
       </c>
       <c r="G50" t="n">
         <v>73.61</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>-2.418149707920121</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-15 00:13</t>
+          <t>2026-05-15 21:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3725,13 +3725,13 @@
         <v>1557</v>
       </c>
       <c r="F51" t="n">
-        <v>1557</v>
+        <v>1528</v>
       </c>
       <c r="G51" t="n">
         <v>1557</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>-1.862556197816313</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-15 00:13</t>
+          <t>2026-05-15 21:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3790,13 +3790,13 @@
         <v>99.48</v>
       </c>
       <c r="F52" t="n">
-        <v>99.48</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="G52" t="n">
         <v>99.48</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>-2.060715721753113</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3833,7 +3833,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-15 00:14</t>
+          <t>2026-05-15 21:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3855,13 +3855,13 @@
         <v>417</v>
       </c>
       <c r="F53" t="n">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="G53" t="n">
         <v>417</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-1.199040767386091</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-15 00:14</t>
+          <t>2026-05-15 21:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3920,13 +3920,13 @@
         <v>20.67</v>
       </c>
       <c r="F54" t="n">
-        <v>20.67</v>
+        <v>19.88</v>
       </c>
       <c r="G54" t="n">
         <v>20.67</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-3.821964199322703</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-15 00:14</t>
+          <t>2026-05-15 21:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3985,13 +3985,13 @@
         <v>266</v>
       </c>
       <c r="F55" t="n">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G55" t="n">
         <v>266</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-3.007518796992481</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-15 00:14</t>
+          <t>2026-05-15 21:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4050,13 +4050,13 @@
         <v>105</v>
       </c>
       <c r="F56" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G56" t="n">
         <v>105</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-3.80952380952381</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -4158,7 +4158,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-15 00:14</t>
+          <t>2026-05-15 21:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4180,13 +4180,13 @@
         <v>1.345</v>
       </c>
       <c r="F58" t="n">
-        <v>1.345</v>
+        <v>1.315</v>
       </c>
       <c r="G58" t="n">
         <v>1.345</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>-2.230483271375467</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -4223,7 +4223,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-15 00:14</t>
+          <t>2026-05-15 14:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4245,13 +4245,13 @@
         <v>10.34</v>
       </c>
       <c r="F59" t="n">
-        <v>10.34</v>
+        <v>10.19</v>
       </c>
       <c r="G59" t="n">
         <v>10.34</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>-1.45067698259188</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-15 00:14</t>
+          <t>2026-05-15 14:07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4310,13 +4310,13 @@
         <v>2.863</v>
       </c>
       <c r="F60" t="n">
-        <v>2.863</v>
+        <v>2.859</v>
       </c>
       <c r="G60" t="n">
         <v>2.863</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>-0.1397135871463501</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -4353,7 +4353,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-15 00:14</t>
+          <t>2026-05-15 21:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4375,13 +4375,13 @@
         <v>68.70999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>68.70999999999999</v>
+        <v>67.63</v>
       </c>
       <c r="G61" t="n">
         <v>68.70999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>-1.571823606461939</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -4418,7 +4418,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 21:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4440,13 +4440,13 @@
         <v>1.453</v>
       </c>
       <c r="F62" t="n">
-        <v>1.453</v>
+        <v>1.429</v>
       </c>
       <c r="G62" t="n">
         <v>1.453</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>-1.651754989676533</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 21:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4505,13 +4505,13 @@
         <v>107</v>
       </c>
       <c r="F63" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G63" t="n">
         <v>107</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>-1.869158878504673</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 21:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4570,13 +4570,13 @@
         <v>10.97</v>
       </c>
       <c r="F64" t="n">
-        <v>10.97</v>
+        <v>10.6</v>
       </c>
       <c r="G64" t="n">
         <v>10.97</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>-3.372835004557894</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -4613,7 +4613,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 21:02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4635,16 +4635,16 @@
         <v>49.75</v>
       </c>
       <c r="F65" t="n">
-        <v>49.75</v>
+        <v>51.15</v>
       </c>
       <c r="G65" t="n">
-        <v>49.75</v>
+        <v>51.7</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>2.814070351758791</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>3.919597989949755</v>
       </c>
       <c r="J65" t="n">
         <v>4.347736833893983</v>
@@ -4678,7 +4678,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 21:02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4700,13 +4700,13 @@
         <v>180</v>
       </c>
       <c r="F66" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G66" t="n">
         <v>180</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>-2.222222222222222</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 21:02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4765,13 +4765,13 @@
         <v>22</v>
       </c>
       <c r="F67" t="n">
-        <v>22</v>
+        <v>20.94</v>
       </c>
       <c r="G67" t="n">
         <v>22</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>-4.818181818181812</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 21:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4830,13 +4830,13 @@
         <v>176</v>
       </c>
       <c r="F68" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G68" t="n">
         <v>176</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>-2.840909090909091</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 21:02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4895,16 +4895,16 @@
         <v>6.281</v>
       </c>
       <c r="F69" t="n">
-        <v>6.281</v>
+        <v>6.346</v>
       </c>
       <c r="G69" t="n">
-        <v>6.281</v>
+        <v>6.346</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1.034867059385455</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1.034867059385455</v>
       </c>
       <c r="J69" t="n">
         <v>1.051502571612002</v>
@@ -4938,7 +4938,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 21:02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4960,13 +4960,13 @@
         <v>130</v>
       </c>
       <c r="F70" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G70" t="n">
         <v>130</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>-2.307692307692308</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-15 00:15</t>
+          <t>2026-05-15 14:08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>75.03</v>
       </c>
       <c r="F72" t="n">
-        <v>75.03</v>
+        <v>76</v>
       </c>
       <c r="G72" t="n">
-        <v>75.03</v>
+        <v>76</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1.292816206850592</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1.292816206850592</v>
       </c>
       <c r="J72" t="n">
         <v>3.422439551749498</v>
@@ -5133,7 +5133,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-15 00:16</t>
+          <t>2026-05-15 21:02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5155,16 +5155,16 @@
         <v>50.03</v>
       </c>
       <c r="F73" t="n">
-        <v>50.03</v>
+        <v>52.76</v>
       </c>
       <c r="G73" t="n">
-        <v>50.03</v>
+        <v>52.76</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>5.456725964421341</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>5.456725964421341</v>
       </c>
       <c r="J73" t="n">
         <v>1.295429222429503</v>
@@ -5198,7 +5198,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-15 00:16</t>
+          <t>2026-05-15 21:02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5220,13 +5220,13 @@
         <v>92.23</v>
       </c>
       <c r="F74" t="n">
-        <v>92.23</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="G74" t="n">
         <v>92.23</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>-1.561314106039247</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-15 00:16</t>
+          <t>2026-05-15 14:08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5285,13 +5285,13 @@
         <v>8.465999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>8.465999999999999</v>
+        <v>8.404</v>
       </c>
       <c r="G75" t="n">
         <v>8.465999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>-0.7323411292227663</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-15 00:16</t>
+          <t>2026-05-15 21:03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5415,13 +5415,13 @@
         <v>27.79</v>
       </c>
       <c r="F77" t="n">
-        <v>27.79</v>
+        <v>26.74</v>
       </c>
       <c r="G77" t="n">
         <v>27.79</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>-3.778337531486148</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -5458,7 +5458,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-15 00:16</t>
+          <t>2026-05-15 21:03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5480,13 +5480,13 @@
         <v>2.064</v>
       </c>
       <c r="F78" t="n">
-        <v>2.064</v>
+        <v>2.042</v>
       </c>
       <c r="G78" t="n">
         <v>2.064</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>-1.065891472868229</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-15 00:16</t>
+          <t>2026-05-15 21:03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5545,13 +5545,13 @@
         <v>206</v>
       </c>
       <c r="F79" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G79" t="n">
         <v>206</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>-2.427184466019417</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 14:09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5610,16 +5610,16 @@
         <v>26.55</v>
       </c>
       <c r="F80" t="n">
-        <v>26.55</v>
+        <v>27.33</v>
       </c>
       <c r="G80" t="n">
-        <v>26.55</v>
+        <v>27.33</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>2.937853107344623</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>2.937853107344623</v>
       </c>
       <c r="J80" t="n">
         <v>2.687664911855825</v>
@@ -5653,7 +5653,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 21:03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5675,13 +5675,13 @@
         <v>148</v>
       </c>
       <c r="F81" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G81" t="n">
         <v>148</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>-2.702702702702703</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -5718,7 +5718,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 21:03</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5740,13 +5740,13 @@
         <v>97.48999999999999</v>
       </c>
       <c r="F82" t="n">
-        <v>97.48999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G82" t="n">
         <v>97.48999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>-2.451533490614422</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 21:03</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5805,16 +5805,16 @@
         <v>93.37</v>
       </c>
       <c r="F83" t="n">
-        <v>93.37</v>
+        <v>99.19</v>
       </c>
       <c r="G83" t="n">
-        <v>93.37</v>
+        <v>99.19</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>6.233265502838163</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>6.233265502838163</v>
       </c>
       <c r="J83" t="n">
         <v>4.588487293283801</v>
@@ -5848,7 +5848,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 21:03</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5870,13 +5870,13 @@
         <v>26.1</v>
       </c>
       <c r="F84" t="n">
-        <v>26.1</v>
+        <v>25.38</v>
       </c>
       <c r="G84" t="n">
         <v>26.1</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>-2.758620689655181</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -5913,7 +5913,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 21:04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5935,13 +5935,13 @@
         <v>122</v>
       </c>
       <c r="F85" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G85" t="n">
         <v>122</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>-4.918032786885246</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 21:04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6000,13 +6000,13 @@
         <v>26.16</v>
       </c>
       <c r="F86" t="n">
-        <v>26.16</v>
+        <v>26.05</v>
       </c>
       <c r="G86" t="n">
         <v>26.16</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>-0.4204892966360834</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -6043,7 +6043,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 21:04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6065,13 +6065,13 @@
         <v>813</v>
       </c>
       <c r="F87" t="n">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="G87" t="n">
         <v>813</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>-1.599015990159901</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -6108,7 +6108,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 21:04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6130,13 +6130,13 @@
         <v>34.14</v>
       </c>
       <c r="F88" t="n">
-        <v>34.14</v>
+        <v>32.98</v>
       </c>
       <c r="G88" t="n">
         <v>34.14</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>-3.397773872290579</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -6173,7 +6173,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-15 00:17</t>
+          <t>2026-05-15 21:04</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6195,13 +6195,13 @@
         <v>12.53</v>
       </c>
       <c r="F89" t="n">
-        <v>12.53</v>
+        <v>12.16</v>
       </c>
       <c r="G89" t="n">
         <v>12.53</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>-2.952913008778924</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-15 00:18</t>
+          <t>2026-05-15 21:04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6260,13 +6260,13 @@
         <v>13.25</v>
       </c>
       <c r="F90" t="n">
-        <v>13.25</v>
+        <v>12.85</v>
       </c>
       <c r="G90" t="n">
         <v>13.25</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>-3.018867924528305</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-15 00:18</t>
+          <t>2026-05-15 21:04</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6325,13 +6325,13 @@
         <v>105</v>
       </c>
       <c r="F91" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G91" t="n">
         <v>105</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>-3.80952380952381</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -6368,7 +6368,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-15 00:18</t>
+          <t>2026-05-15 21:04</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6390,13 +6390,13 @@
         <v>227</v>
       </c>
       <c r="F92" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G92" t="n">
         <v>227</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>-3.524229074889868</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -6433,7 +6433,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-15 00:18</t>
+          <t>2026-05-15 21:04</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6455,13 +6455,13 @@
         <v>2.83</v>
       </c>
       <c r="F93" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="G93" t="n">
         <v>2.83</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>-2.826855123674914</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -6563,7 +6563,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-15 00:18</t>
+          <t>2026-05-15 21:05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6585,13 +6585,13 @@
         <v>122</v>
       </c>
       <c r="F95" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G95" t="n">
         <v>122</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>-0.819672131147541</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -6628,7 +6628,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-15 00:18</t>
+          <t>2026-05-15 21:05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6650,16 +6650,16 @@
         <v>15.02</v>
       </c>
       <c r="F96" t="n">
-        <v>15.02</v>
+        <v>15.22</v>
       </c>
       <c r="G96" t="n">
-        <v>15.02</v>
+        <v>15.38</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1.331557922769647</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2.396804260985361</v>
       </c>
       <c r="J96" t="n">
         <v>2.664253498944049</v>
@@ -6693,7 +6693,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-15 00:18</t>
+          <t>2026-05-15 21:05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6715,13 +6715,13 @@
         <v>113</v>
       </c>
       <c r="F97" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G97" t="n">
         <v>113</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>-2.654867256637168</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
@@ -6758,7 +6758,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-15 00:18</t>
+          <t>2026-05-15 21:05</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6780,13 +6780,13 @@
         <v>188</v>
       </c>
       <c r="F98" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G98" t="n">
         <v>188</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>-1.595744680851064</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -7018,7 +7018,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-15 00:36</t>
+          <t>2026-05-15 21:02</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7040,13 +7040,13 @@
         <v>1.975</v>
       </c>
       <c r="F102" t="n">
-        <v>1.975</v>
+        <v>1.954</v>
       </c>
       <c r="G102" t="n">
         <v>1.975</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>-1.063291139240513</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -7205,6 +7205,2476 @@
         </is>
       </c>
       <c r="Q104" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>A/KRW</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>135</v>
+      </c>
+      <c r="F105" t="n">
+        <v>133</v>
+      </c>
+      <c r="G105" t="n">
+        <v>135</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-1.481481481481482</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>4.808215451577813</v>
+      </c>
+      <c r="K105" t="n">
+        <v>128.425</v>
+      </c>
+      <c r="L105" t="n">
+        <v>122.5333333333333</v>
+      </c>
+      <c r="M105" t="n">
+        <v>181.4054054054054</v>
+      </c>
+      <c r="N105" t="n">
+        <v>7</v>
+      </c>
+      <c r="O105" t="n">
+        <v>50</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ZRX/KRW</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>170</v>
+      </c>
+      <c r="F106" t="n">
+        <v>168</v>
+      </c>
+      <c r="G106" t="n">
+        <v>170</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-1.176470588235294</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>3.042934556065032</v>
+      </c>
+      <c r="K106" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="L106" t="n">
+        <v>159.9333333333333</v>
+      </c>
+      <c r="M106" t="n">
+        <v>183.4432432432432</v>
+      </c>
+      <c r="N106" t="n">
+        <v>7</v>
+      </c>
+      <c r="O106" t="n">
+        <v>50</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:10</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>FCT2/KRW</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="F107" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G107" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-0.6479481641468736</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1.296267514705161</v>
+      </c>
+      <c r="K107" t="n">
+        <v>18.8285</v>
+      </c>
+      <c r="L107" t="n">
+        <v>18.58755555555556</v>
+      </c>
+      <c r="M107" t="n">
+        <v>19.25832432432432</v>
+      </c>
+      <c r="N107" t="n">
+        <v>6</v>
+      </c>
+      <c r="O107" t="n">
+        <v>50</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:02</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AERGO/KRW</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="F108" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="G108" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.6032099177350947</v>
+      </c>
+      <c r="K108" t="n">
+        <v>81.74525</v>
+      </c>
+      <c r="L108" t="n">
+        <v>81.25511111111111</v>
+      </c>
+      <c r="M108" t="n">
+        <v>85.67535135135135</v>
+      </c>
+      <c r="N108" t="n">
+        <v>7</v>
+      </c>
+      <c r="O108" t="n">
+        <v>50</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:10</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MVC/KRW</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.439</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2.439</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.04101722723543436</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.04101722723543436</v>
+      </c>
+      <c r="J109" t="n">
+        <v>3.276552725753929</v>
+      </c>
+      <c r="K109" t="n">
+        <v>2.41775</v>
+      </c>
+      <c r="L109" t="n">
+        <v>2.341044444444444</v>
+      </c>
+      <c r="M109" t="n">
+        <v>2.699043243243243</v>
+      </c>
+      <c r="N109" t="n">
+        <v>6</v>
+      </c>
+      <c r="O109" t="n">
+        <v>50</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:10</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>GRT/KRW</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="F110" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G110" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1.558694593278131</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1.558694593278131</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1.022698015167123</v>
+      </c>
+      <c r="K110" t="n">
+        <v>37.5885</v>
+      </c>
+      <c r="L110" t="n">
+        <v>37.97688888888889</v>
+      </c>
+      <c r="M110" t="n">
+        <v>49.66335135135134</v>
+      </c>
+      <c r="N110" t="n">
+        <v>10</v>
+      </c>
+      <c r="O110" t="n">
+        <v>50</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MAPO/KRW</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>4.792</v>
+      </c>
+      <c r="F111" t="n">
+        <v>4.815</v>
+      </c>
+      <c r="G111" t="n">
+        <v>4.815</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.479966611018376</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.479966611018376</v>
+      </c>
+      <c r="J111" t="n">
+        <v>3.030976564856005</v>
+      </c>
+      <c r="K111" t="n">
+        <v>4.82325</v>
+      </c>
+      <c r="L111" t="n">
+        <v>4.974011111111111</v>
+      </c>
+      <c r="M111" t="n">
+        <v>5.50025945945946</v>
+      </c>
+      <c r="N111" t="n">
+        <v>10</v>
+      </c>
+      <c r="O111" t="n">
+        <v>50</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:11</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>WOO/KRW</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="F112" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="G112" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-2.029191883232468</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>4.440255208354989</v>
+      </c>
+      <c r="K112" t="n">
+        <v>27.90075</v>
+      </c>
+      <c r="L112" t="n">
+        <v>26.71455555555556</v>
+      </c>
+      <c r="M112" t="n">
+        <v>32.54491891891892</v>
+      </c>
+      <c r="N112" t="n">
+        <v>6</v>
+      </c>
+      <c r="O112" t="n">
+        <v>50</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:11</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>XLM/KRW</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>238</v>
+      </c>
+      <c r="F113" t="n">
+        <v>236</v>
+      </c>
+      <c r="G113" t="n">
+        <v>238</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-0.8403361344537815</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.2320665410596905</v>
+      </c>
+      <c r="K113" t="n">
+        <v>242.35</v>
+      </c>
+      <c r="L113" t="n">
+        <v>241.7888888888889</v>
+      </c>
+      <c r="M113" t="n">
+        <v>285.9405405405406</v>
+      </c>
+      <c r="N113" t="n">
+        <v>9</v>
+      </c>
+      <c r="O113" t="n">
+        <v>50</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:11</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CTK/KRW</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>S+</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>293</v>
+      </c>
+      <c r="F114" t="n">
+        <v>287</v>
+      </c>
+      <c r="G114" t="n">
+        <v>293</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-2.04778156996587</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.1615910503418286</v>
+      </c>
+      <c r="K114" t="n">
+        <v>268.6</v>
+      </c>
+      <c r="L114" t="n">
+        <v>268.1666666666667</v>
+      </c>
+      <c r="M114" t="n">
+        <v>324.1027027027027</v>
+      </c>
+      <c r="N114" t="n">
+        <v>8</v>
+      </c>
+      <c r="O114" t="n">
+        <v>50</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:12</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>REQ/KRW</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>102</v>
+      </c>
+      <c r="F115" t="n">
+        <v>102</v>
+      </c>
+      <c r="G115" t="n">
+        <v>102</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>4.515947344648756</v>
+      </c>
+      <c r="K115" t="n">
+        <v>106.69975</v>
+      </c>
+      <c r="L115" t="n">
+        <v>102.0894444444444</v>
+      </c>
+      <c r="M115" t="n">
+        <v>129.0110810810811</v>
+      </c>
+      <c r="N115" t="n">
+        <v>7</v>
+      </c>
+      <c r="O115" t="n">
+        <v>50</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:12</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>HBAR/KRW</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>140</v>
+      </c>
+      <c r="F116" t="n">
+        <v>138</v>
+      </c>
+      <c r="G116" t="n">
+        <v>140</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2.859042553191486</v>
+      </c>
+      <c r="K116" t="n">
+        <v>133.925</v>
+      </c>
+      <c r="L116" t="n">
+        <v>137.8666666666667</v>
+      </c>
+      <c r="M116" t="n">
+        <v>158.6054054054054</v>
+      </c>
+      <c r="N116" t="n">
+        <v>7</v>
+      </c>
+      <c r="O116" t="n">
+        <v>50</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TAVA/KRW</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6.276</v>
+      </c>
+      <c r="F117" t="n">
+        <v>6.263</v>
+      </c>
+      <c r="G117" t="n">
+        <v>6.276</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-0.2071383046526434</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.723710165644407</v>
+      </c>
+      <c r="K117" t="n">
+        <v>6.325975</v>
+      </c>
+      <c r="L117" t="n">
+        <v>6.280522222222221</v>
+      </c>
+      <c r="M117" t="n">
+        <v>7.401886486486488</v>
+      </c>
+      <c r="N117" t="n">
+        <v>7</v>
+      </c>
+      <c r="O117" t="n">
+        <v>50</v>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>WNCG/KRW</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>S+</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>8.714</v>
+      </c>
+      <c r="F118" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="G118" t="n">
+        <v>8.714</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-0.7344503098462251</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.1575708442847052</v>
+      </c>
+      <c r="K118" t="n">
+        <v>8.196774999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>8.209711111111112</v>
+      </c>
+      <c r="M118" t="n">
+        <v>10.13341081081081</v>
+      </c>
+      <c r="N118" t="n">
+        <v>9</v>
+      </c>
+      <c r="O118" t="n">
+        <v>50</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>STX/KRW</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>388</v>
+      </c>
+      <c r="F119" t="n">
+        <v>384</v>
+      </c>
+      <c r="G119" t="n">
+        <v>388</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-1.030927835051546</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2.605154350732107</v>
+      </c>
+      <c r="K119" t="n">
+        <v>348.1</v>
+      </c>
+      <c r="L119" t="n">
+        <v>357.4111111111111</v>
+      </c>
+      <c r="M119" t="n">
+        <v>405.6108108108108</v>
+      </c>
+      <c r="N119" t="n">
+        <v>9</v>
+      </c>
+      <c r="O119" t="n">
+        <v>50</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>IMX/KRW</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>293</v>
+      </c>
+      <c r="F120" t="n">
+        <v>293</v>
+      </c>
+      <c r="G120" t="n">
+        <v>293</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>3.572752119331084</v>
+      </c>
+      <c r="K120" t="n">
+        <v>248.425</v>
+      </c>
+      <c r="L120" t="n">
+        <v>239.8555555555556</v>
+      </c>
+      <c r="M120" t="n">
+        <v>316.9135135135135</v>
+      </c>
+      <c r="N120" t="n">
+        <v>9</v>
+      </c>
+      <c r="O120" t="n">
+        <v>50</v>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:13</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ASTR/KRW</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="F121" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="G121" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2.323780015491872</v>
+      </c>
+      <c r="I121" t="n">
+        <v>2.323780015491872</v>
+      </c>
+      <c r="J121" t="n">
+        <v>4.827691485707735</v>
+      </c>
+      <c r="K121" t="n">
+        <v>12.208</v>
+      </c>
+      <c r="L121" t="n">
+        <v>11.64577777777778</v>
+      </c>
+      <c r="M121" t="n">
+        <v>14.06875675675676</v>
+      </c>
+      <c r="N121" t="n">
+        <v>6</v>
+      </c>
+      <c r="O121" t="n">
+        <v>50</v>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>RVN/KRW</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>8.804</v>
+      </c>
+      <c r="F122" t="n">
+        <v>8.702999999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>8.804</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-1.147205815538402</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1.926348347187314</v>
+      </c>
+      <c r="K122" t="n">
+        <v>8.787749999999999</v>
+      </c>
+      <c r="L122" t="n">
+        <v>8.621666666666666</v>
+      </c>
+      <c r="M122" t="n">
+        <v>9.840632432432432</v>
+      </c>
+      <c r="N122" t="n">
+        <v>7</v>
+      </c>
+      <c r="O122" t="n">
+        <v>50</v>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>STORJ/KRW</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>158</v>
+      </c>
+      <c r="F123" t="n">
+        <v>157</v>
+      </c>
+      <c r="G123" t="n">
+        <v>158</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-0.6329113924050633</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>3.796070667072801</v>
+      </c>
+      <c r="K123" t="n">
+        <v>151.45</v>
+      </c>
+      <c r="L123" t="n">
+        <v>145.9111111111111</v>
+      </c>
+      <c r="M123" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="N123" t="n">
+        <v>7</v>
+      </c>
+      <c r="O123" t="n">
+        <v>50</v>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:01</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MNT/KRW</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1018</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1003</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1018</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-1.473477406679764</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2.142594203868553</v>
+      </c>
+      <c r="K124" t="n">
+        <v>974.725</v>
+      </c>
+      <c r="L124" t="n">
+        <v>996.0666666666667</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1234.389189189189</v>
+      </c>
+      <c r="N124" t="n">
+        <v>6</v>
+      </c>
+      <c r="O124" t="n">
+        <v>50</v>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:01</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>NEO/KRW</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>4591</v>
+      </c>
+      <c r="F125" t="n">
+        <v>4541</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4591</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-1.089087344805053</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>4.41541667453957</v>
+      </c>
+      <c r="K125" t="n">
+        <v>4298.075</v>
+      </c>
+      <c r="L125" t="n">
+        <v>4116.322222222222</v>
+      </c>
+      <c r="M125" t="n">
+        <v>4898.65945945946</v>
+      </c>
+      <c r="N125" t="n">
+        <v>6</v>
+      </c>
+      <c r="O125" t="n">
+        <v>50</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:01</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>GAS/KRW</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>2472</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2447</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2472</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-1.011326860841424</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>3.090747199955822</v>
+      </c>
+      <c r="K126" t="n">
+        <v>2489.275</v>
+      </c>
+      <c r="L126" t="n">
+        <v>2414.644444444445</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2707.989189189189</v>
+      </c>
+      <c r="N126" t="n">
+        <v>7</v>
+      </c>
+      <c r="O126" t="n">
+        <v>50</v>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:01</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>HUNT/KRW</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>S+</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>157</v>
+      </c>
+      <c r="F127" t="n">
+        <v>155</v>
+      </c>
+      <c r="G127" t="n">
+        <v>157</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-1.273885350318471</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1.711182203705092</v>
+      </c>
+      <c r="K127" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="L127" t="n">
+        <v>149.3444444444444</v>
+      </c>
+      <c r="M127" t="n">
+        <v>178.9513513513513</v>
+      </c>
+      <c r="N127" t="n">
+        <v>8</v>
+      </c>
+      <c r="O127" t="n">
+        <v>50</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:01</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>KAVA/KRW</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="F128" t="n">
+        <v>90.23</v>
+      </c>
+      <c r="G128" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-1.987834021290461</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>4.077929945005983</v>
+      </c>
+      <c r="K128" t="n">
+        <v>87.62424999999999</v>
+      </c>
+      <c r="L128" t="n">
+        <v>84.191</v>
+      </c>
+      <c r="M128" t="n">
+        <v>110.3837837837838</v>
+      </c>
+      <c r="N128" t="n">
+        <v>7</v>
+      </c>
+      <c r="O128" t="n">
+        <v>50</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:48</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AUCTION/KRW</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>7235</v>
+      </c>
+      <c r="F129" t="n">
+        <v>7195</v>
+      </c>
+      <c r="G129" t="n">
+        <v>7235</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-0.55286800276434</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.4233619344773734</v>
+      </c>
+      <c r="K129" t="n">
+        <v>7152.375</v>
+      </c>
+      <c r="L129" t="n">
+        <v>7122.222222222223</v>
+      </c>
+      <c r="M129" t="n">
+        <v>7574.756756756757</v>
+      </c>
+      <c r="N129" t="n">
+        <v>7</v>
+      </c>
+      <c r="O129" t="n">
+        <v>50</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:02</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>XAI/KRW</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="F130" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="G130" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-1.906898485698261</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>3.986210381393172</v>
+      </c>
+      <c r="K130" t="n">
+        <v>15.77725</v>
+      </c>
+      <c r="L130" t="n">
+        <v>15.17244444444444</v>
+      </c>
+      <c r="M130" t="n">
+        <v>19.84572972972973</v>
+      </c>
+      <c r="N130" t="n">
+        <v>8</v>
+      </c>
+      <c r="O130" t="n">
+        <v>50</v>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:02</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ATH/KRW</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>9.673</v>
+      </c>
+      <c r="F131" t="n">
+        <v>9.516</v>
+      </c>
+      <c r="G131" t="n">
+        <v>9.673</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-1.623074537372067</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1.111673206211548</v>
+      </c>
+      <c r="K131" t="n">
+        <v>9.263375</v>
+      </c>
+      <c r="L131" t="n">
+        <v>9.367511111111112</v>
+      </c>
+      <c r="M131" t="n">
+        <v>13.28852972972973</v>
+      </c>
+      <c r="N131" t="n">
+        <v>7</v>
+      </c>
+      <c r="O131" t="n">
+        <v>50</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:02</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>EIGEN/KRW</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>322</v>
+      </c>
+      <c r="F132" t="n">
+        <v>316</v>
+      </c>
+      <c r="G132" t="n">
+        <v>322</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-1.863354037267081</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.8669647172547069</v>
+      </c>
+      <c r="K132" t="n">
+        <v>273.475</v>
+      </c>
+      <c r="L132" t="n">
+        <v>275.8666666666667</v>
+      </c>
+      <c r="M132" t="n">
+        <v>458.9081081081081</v>
+      </c>
+      <c r="N132" t="n">
+        <v>10</v>
+      </c>
+      <c r="O132" t="n">
+        <v>50</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:02</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ORDER/KRW</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>82.83</v>
+      </c>
+      <c r="F133" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="G133" t="n">
+        <v>82.83</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-0.09658336351563238</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>3.476189254617209</v>
+      </c>
+      <c r="K133" t="n">
+        <v>85.1555</v>
+      </c>
+      <c r="L133" t="n">
+        <v>82.29477777777778</v>
+      </c>
+      <c r="M133" t="n">
+        <v>112.8787567567568</v>
+      </c>
+      <c r="N133" t="n">
+        <v>7</v>
+      </c>
+      <c r="O133" t="n">
+        <v>50</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:03</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>HP/KRW</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="F134" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="G134" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-1.237031125299277</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>3.621243776773011</v>
+      </c>
+      <c r="K134" t="n">
+        <v>23.424</v>
+      </c>
+      <c r="L134" t="n">
+        <v>24.30411111111111</v>
+      </c>
+      <c r="M134" t="n">
+        <v>29.32091891891892</v>
+      </c>
+      <c r="N134" t="n">
+        <v>9</v>
+      </c>
+      <c r="O134" t="n">
+        <v>50</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:04</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FORT/KRW</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="F135" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="G135" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-1.999200319872051</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>3.888194800475847</v>
+      </c>
+      <c r="K135" t="n">
+        <v>23.1905</v>
+      </c>
+      <c r="L135" t="n">
+        <v>22.32255555555556</v>
+      </c>
+      <c r="M135" t="n">
+        <v>27.13027027027027</v>
+      </c>
+      <c r="N135" t="n">
+        <v>7</v>
+      </c>
+      <c r="O135" t="n">
+        <v>50</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:19</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>FF/KRW</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>118</v>
+      </c>
+      <c r="F136" t="n">
+        <v>118</v>
+      </c>
+      <c r="G136" t="n">
+        <v>118</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2.349376427191292</v>
+      </c>
+      <c r="K136" t="n">
+        <v>105.62575</v>
+      </c>
+      <c r="L136" t="n">
+        <v>108.167</v>
+      </c>
+      <c r="M136" t="n">
+        <v>129.0866486486486</v>
+      </c>
+      <c r="N136" t="n">
+        <v>7</v>
+      </c>
+      <c r="O136" t="n">
+        <v>44</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:05</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SOMI/KRW</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>259</v>
+      </c>
+      <c r="F137" t="n">
+        <v>256</v>
+      </c>
+      <c r="G137" t="n">
+        <v>259</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-1.158301158301158</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1.989734425003122</v>
+      </c>
+      <c r="K137" t="n">
+        <v>262.025</v>
+      </c>
+      <c r="L137" t="n">
+        <v>267.3444444444444</v>
+      </c>
+      <c r="M137" t="n">
+        <v>318.7783783783784</v>
+      </c>
+      <c r="N137" t="n">
+        <v>7</v>
+      </c>
+      <c r="O137" t="n">
+        <v>42</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SUI/KRW</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1719</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1679</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1719</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-2.326934264107039</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>3.110283498681402</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1459.675</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1415.644444444444</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1821.448648648649</v>
+      </c>
+      <c r="N138" t="n">
+        <v>9</v>
+      </c>
+      <c r="O138" t="n">
+        <v>50</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>MAV/KRW</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="F139" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="G139" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5724350506384809</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.5724350506384809</v>
+      </c>
+      <c r="J139" t="n">
+        <v>4.990898058252431</v>
+      </c>
+      <c r="K139" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="L139" t="n">
+        <v>21.97333333333333</v>
+      </c>
+      <c r="M139" t="n">
+        <v>30.73945945945946</v>
+      </c>
+      <c r="N139" t="n">
+        <v>8</v>
+      </c>
+      <c r="O139" t="n">
+        <v>50</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:02</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>RON/KRW</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>148</v>
+      </c>
+      <c r="F140" t="n">
+        <v>148</v>
+      </c>
+      <c r="G140" t="n">
+        <v>148</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1.083117494702141</v>
+      </c>
+      <c r="K140" t="n">
+        <v>143.1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>141.5666666666667</v>
+      </c>
+      <c r="M140" t="n">
+        <v>188.1891891891892</v>
+      </c>
+      <c r="N140" t="n">
+        <v>9</v>
+      </c>
+      <c r="O140" t="n">
+        <v>50</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:22</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>BNT/KRW</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>S+</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>501</v>
+      </c>
+      <c r="F141" t="n">
+        <v>501</v>
+      </c>
+      <c r="G141" t="n">
+        <v>501</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>4.829864841232167</v>
+      </c>
+      <c r="K141" t="n">
+        <v>466.225</v>
+      </c>
+      <c r="L141" t="n">
+        <v>444.7444444444445</v>
+      </c>
+      <c r="M141" t="n">
+        <v>529.2540540540541</v>
+      </c>
+      <c r="N141" t="n">
+        <v>6</v>
+      </c>
+      <c r="O141" t="n">
+        <v>50</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-15 21:50</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>RISE1</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NXPC/KRW</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>511</v>
+      </c>
+      <c r="F142" t="n">
+        <v>511</v>
+      </c>
+      <c r="G142" t="n">
+        <v>511</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>4.586728754365539</v>
+      </c>
+      <c r="K142" t="n">
+        <v>449.2</v>
+      </c>
+      <c r="L142" t="n">
+        <v>429.5</v>
+      </c>
+      <c r="M142" t="n">
+        <v>506.8864864864865</v>
+      </c>
+      <c r="N142" t="n">
+        <v>6</v>
+      </c>
+      <c r="O142" t="n">
+        <v>46</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>90_Touch</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
